--- a/students.xlsx
+++ b/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>Student Name</t>
   </si>
@@ -25,46 +25,160 @@
     <t>Équipe</t>
   </si>
   <si>
-    <t>Ahmed Ali</t>
-  </si>
-  <si>
-    <t>4A</t>
+    <t>Hania Hisham</t>
   </si>
   <si>
     <t>+201001234567</t>
   </si>
   <si>
-    <t>Jaune</t>
-  </si>
-  <si>
-    <t>Fatima Hassan</t>
-  </si>
-  <si>
-    <t>4B</t>
+    <t>Perla Kamel</t>
   </si>
   <si>
     <t>01012345678</t>
   </si>
   <si>
-    <t>Rouge</t>
-  </si>
-  <si>
-    <t>Mohamed Ibrahim</t>
-  </si>
-  <si>
-    <t>5A</t>
+    <t>Judy Islam</t>
   </si>
   <si>
     <t>+201112345678</t>
   </si>
   <si>
-    <t>Vert</t>
-  </si>
-  <si>
-    <t>Sara Youssef</t>
-  </si>
-  <si>
-    <t>5B</t>
+    <t>Angelina Michael</t>
+  </si>
+  <si>
+    <t>Taiba Fady</t>
+  </si>
+  <si>
+    <t>Hayat Fady</t>
+  </si>
+  <si>
+    <t>Renata Radi Ramzi</t>
+  </si>
+  <si>
+    <t>Karin Baher</t>
+  </si>
+  <si>
+    <t>Celine Baher</t>
+  </si>
+  <si>
+    <t>Selena Osama</t>
+  </si>
+  <si>
+    <t>Lily Wahib</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Malika Mostafa</t>
+  </si>
+  <si>
+    <t>Tia Hussein</t>
+  </si>
+  <si>
+    <t>Perla Fady Azmi</t>
+  </si>
+  <si>
+    <t>Perla Michael Khalaf</t>
+  </si>
+  <si>
+    <t>Zeina Ahmed</t>
+  </si>
+  <si>
+    <t>Selena Samah</t>
+  </si>
+  <si>
+    <t>Angelina Mina</t>
+  </si>
+  <si>
+    <t>Alia Markos</t>
+  </si>
+  <si>
+    <t>Habiba Wael</t>
+  </si>
+  <si>
+    <t>Jasmine Ahmed</t>
+  </si>
+  <si>
+    <t>Howaida Amir</t>
+  </si>
+  <si>
+    <t>Ayla Shahab</t>
+  </si>
+  <si>
+    <t>Amelia Ehhab</t>
+  </si>
+  <si>
+    <t>Fatima Mohamed Badawi</t>
+  </si>
+  <si>
+    <t>Fatima Ammar</t>
+  </si>
+  <si>
+    <t>Marley Anton</t>
+  </si>
+  <si>
+    <t>Maria Maher</t>
+  </si>
+  <si>
+    <t>Sara Sherif</t>
+  </si>
+  <si>
+    <t>Clara Bishoy</t>
+  </si>
+  <si>
+    <t>Asil Ibrahim Khaled</t>
+  </si>
+  <si>
+    <t>Carla Fady Azmi</t>
+  </si>
+  <si>
+    <t>Lareen Ramez Waseem</t>
+  </si>
+  <si>
+    <t>Tia Zakaria</t>
+  </si>
+  <si>
+    <t>Lily Mohamed Abdelrahman</t>
+  </si>
+  <si>
+    <t>Dima Mohamed Ali</t>
+  </si>
+  <si>
+    <t>Lama Osama</t>
+  </si>
+  <si>
+    <t>Julie Ramy</t>
+  </si>
+  <si>
+    <t>Talia Hassan</t>
+  </si>
+  <si>
+    <t>Hager Tamer</t>
+  </si>
+  <si>
+    <t>Mariam Badawi</t>
+  </si>
+  <si>
+    <t>Mirola Wagdy</t>
+  </si>
+  <si>
+    <t>Mariam Asim</t>
+  </si>
+  <si>
+    <t>Mariam Amara</t>
+  </si>
+  <si>
+    <t>Retaj Ahmed</t>
+  </si>
+  <si>
+    <t>Hala Tamer</t>
+  </si>
+  <si>
+    <t>Khadija Wael</t>
+  </si>
+  <si>
+    <t>Sara Samuel</t>
   </si>
 </sst>
 </file>
@@ -343,184 +457,583 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+      <c r="D2" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>6.0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B11" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4"/>
-    </row>
-    <row r="6">
-      <c r="C6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8">
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12">
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="4"/>
+      <c r="D12" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C13" s="4"/>
+      <c r="D13" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C14" s="4"/>
+      <c r="D14" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C15" s="4"/>
+      <c r="D15" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C16" s="4"/>
+      <c r="D16" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C17" s="4"/>
+      <c r="D17" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C18" s="4"/>
+      <c r="D18" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C19" s="4"/>
+      <c r="D19" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C20" s="4"/>
+      <c r="D20" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C21" s="4"/>
+      <c r="D21" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C22" s="4"/>
+      <c r="D22" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C23" s="4"/>
+      <c r="D23" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C24" s="4"/>
+      <c r="D24" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C25" s="4"/>
+      <c r="D25" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C26" s="4"/>
+      <c r="D26" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C27" s="4"/>
+      <c r="D27" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C28" s="4"/>
+      <c r="D28" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C29" s="4"/>
+      <c r="D29" s="1">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C30" s="4"/>
+      <c r="D30" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C31" s="4"/>
+      <c r="D31" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C32" s="4"/>
+      <c r="D32" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C33" s="4"/>
+      <c r="D33" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C34" s="4"/>
+      <c r="D34" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C35" s="4"/>
+      <c r="D35" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C36" s="4"/>
+      <c r="D36" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C37" s="4"/>
+      <c r="D37" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C38" s="4"/>
+      <c r="D38" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1">
+        <v>4.0</v>
+      </c>
       <c r="C39" s="4"/>
+      <c r="D39" s="1">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C40" s="4"/>
+      <c r="D40" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C41" s="4"/>
+      <c r="D41" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C42" s="4"/>
+      <c r="D42" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C43" s="4"/>
+      <c r="D43" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C44" s="4"/>
+      <c r="D44" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C45" s="4"/>
+      <c r="D45" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C46" s="4"/>
+      <c r="D46" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C47" s="4"/>
+      <c r="D47" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C48" s="4"/>
+      <c r="D48" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C49" s="4"/>
+      <c r="D49" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="50">
       <c r="C50" s="4"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Student Name</t>
   </si>
@@ -28,157 +28,151 @@
     <t>Hania Hisham</t>
   </si>
   <si>
-    <t>+201001234567</t>
-  </si>
-  <si>
     <t>Perla Kamel</t>
   </si>
   <si>
-    <t>01012345678</t>
-  </si>
-  <si>
-    <t>Judy Islam</t>
-  </si>
-  <si>
-    <t>+201112345678</t>
+    <t>Joudy Islam</t>
   </si>
   <si>
     <t>Angelina Michael</t>
   </si>
   <si>
-    <t>Taiba Fady</t>
-  </si>
-  <si>
-    <t>Hayat Fady</t>
+    <t>TIba Fady</t>
+  </si>
+  <si>
+    <t>Hayah Fady</t>
   </si>
   <si>
     <t>Renata Radi Ramzi</t>
   </si>
   <si>
-    <t>Karin Baher</t>
+    <t>Carine Baher</t>
   </si>
   <si>
     <t>Celine Baher</t>
   </si>
   <si>
-    <t>Selena Osama</t>
-  </si>
-  <si>
-    <t>Lily Wahib</t>
+    <t>Celina Osama</t>
+  </si>
+  <si>
+    <t>Laila Wahb</t>
+  </si>
+  <si>
+    <t>Malika Mostafa</t>
+  </si>
+  <si>
+    <t>Tia Hussein</t>
+  </si>
+  <si>
+    <t>Perla Fady Azmi</t>
+  </si>
+  <si>
+    <t>Perla Michael Khalaf</t>
+  </si>
+  <si>
+    <t>Zeina Ahmed</t>
+  </si>
+  <si>
+    <t>Celina Sameh</t>
+  </si>
+  <si>
+    <t>Angelina Mina</t>
+  </si>
+  <si>
+    <t>Ema Morkos</t>
+  </si>
+  <si>
+    <t>Habiba Wael</t>
+  </si>
+  <si>
+    <t>Jasmine Ahmed</t>
+  </si>
+  <si>
+    <t>Mouira Amir</t>
+  </si>
+  <si>
+    <t>Ella Shehab</t>
+  </si>
+  <si>
+    <t>Emilia Ehab</t>
+  </si>
+  <si>
+    <t>Fatima Mohamed Badawi</t>
+  </si>
+  <si>
+    <t>Fatima Ammar</t>
+  </si>
+  <si>
+    <t>Marley Anton</t>
+  </si>
+  <si>
+    <t>Maria Maher</t>
+  </si>
+  <si>
+    <t>Sara Cherif</t>
+  </si>
+  <si>
+    <t>Clara Bishoy</t>
+  </si>
+  <si>
+    <t>Assil Ibrahim Khaled</t>
+  </si>
+  <si>
+    <t>Carla Fady Azmi</t>
+  </si>
+  <si>
+    <t>Laren Ramez Wassim</t>
+  </si>
+  <si>
+    <t>Tia Zakaria</t>
+  </si>
+  <si>
+    <t>Laila Mohamed Abdelrahman</t>
+  </si>
+  <si>
+    <t>Dima Mohamed Ali</t>
+  </si>
+  <si>
+    <t>Lama Osama</t>
+  </si>
+  <si>
+    <t>Julie Ramy</t>
+  </si>
+  <si>
+    <t>Talia Hussein</t>
+  </si>
+  <si>
+    <t>Hagar Tamer</t>
+  </si>
+  <si>
+    <t>Mariam Badawi</t>
+  </si>
+  <si>
+    <t>Mirola Wagdy</t>
+  </si>
+  <si>
+    <t>Mariam Assem</t>
+  </si>
+  <si>
+    <t>Mariam Emara</t>
+  </si>
+  <si>
+    <t>Ritaj Ahmed</t>
+  </si>
+  <si>
+    <t>Hala Tamer</t>
+  </si>
+  <si>
+    <t>Khadija Wael</t>
+  </si>
+  <si>
+    <t>Sara Samuel</t>
+  </si>
+  <si>
+    <t>Roba Mohamed</t>
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Malika Mostafa</t>
-  </si>
-  <si>
-    <t>Tia Hussein</t>
-  </si>
-  <si>
-    <t>Perla Fady Azmi</t>
-  </si>
-  <si>
-    <t>Perla Michael Khalaf</t>
-  </si>
-  <si>
-    <t>Zeina Ahmed</t>
-  </si>
-  <si>
-    <t>Selena Samah</t>
-  </si>
-  <si>
-    <t>Angelina Mina</t>
-  </si>
-  <si>
-    <t>Alia Markos</t>
-  </si>
-  <si>
-    <t>Habiba Wael</t>
-  </si>
-  <si>
-    <t>Jasmine Ahmed</t>
-  </si>
-  <si>
-    <t>Howaida Amir</t>
-  </si>
-  <si>
-    <t>Ayla Shahab</t>
-  </si>
-  <si>
-    <t>Amelia Ehhab</t>
-  </si>
-  <si>
-    <t>Fatima Mohamed Badawi</t>
-  </si>
-  <si>
-    <t>Fatima Ammar</t>
-  </si>
-  <si>
-    <t>Marley Anton</t>
-  </si>
-  <si>
-    <t>Maria Maher</t>
-  </si>
-  <si>
-    <t>Sara Sherif</t>
-  </si>
-  <si>
-    <t>Clara Bishoy</t>
-  </si>
-  <si>
-    <t>Asil Ibrahim Khaled</t>
-  </si>
-  <si>
-    <t>Carla Fady Azmi</t>
-  </si>
-  <si>
-    <t>Lareen Ramez Waseem</t>
-  </si>
-  <si>
-    <t>Tia Zakaria</t>
-  </si>
-  <si>
-    <t>Lily Mohamed Abdelrahman</t>
-  </si>
-  <si>
-    <t>Dima Mohamed Ali</t>
-  </si>
-  <si>
-    <t>Lama Osama</t>
-  </si>
-  <si>
-    <t>Julie Ramy</t>
-  </si>
-  <si>
-    <t>Talia Hassan</t>
-  </si>
-  <si>
-    <t>Hager Tamer</t>
-  </si>
-  <si>
-    <t>Mariam Badawi</t>
-  </si>
-  <si>
-    <t>Mirola Wagdy</t>
-  </si>
-  <si>
-    <t>Mariam Asim</t>
-  </si>
-  <si>
-    <t>Mariam Amara</t>
-  </si>
-  <si>
-    <t>Retaj Ahmed</t>
-  </si>
-  <si>
-    <t>Hala Tamer</t>
-  </si>
-  <si>
-    <t>Khadija Wael</t>
-  </si>
-  <si>
-    <t>Sara Samuel</t>
   </si>
 </sst>
 </file>
@@ -212,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -220,9 +214,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -460,3433 +451,3436 @@
       <c r="B2" s="1">
         <v>6.0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1">
         <v>6.0</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>6.0</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1">
         <v>6.0</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
         <v>6.0</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
         <v>6.0</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1">
         <v>6.0</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1">
         <v>6.0</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1">
         <v>6.0</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1">
         <v>6.0</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="1">
         <v>1.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B12" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="B13" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="B14" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C14" s="3"/>
       <c r="D14" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="B16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="B17" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="B18" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C18" s="3"/>
       <c r="D18" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="B19" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C19" s="3"/>
       <c r="D19" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="B21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C21" s="3"/>
       <c r="D21" s="1">
         <v>2.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1">
         <v>4.0</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="2"/>
       <c r="D22" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1">
         <v>4.0</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1">
         <v>4.0</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="3"/>
       <c r="D24" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B25" s="1">
         <v>4.0</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="3"/>
       <c r="D25" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B26" s="1">
         <v>4.0</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="3"/>
       <c r="D26" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B27" s="1">
         <v>4.0</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="3"/>
       <c r="D27" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1">
         <v>4.0</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="3"/>
       <c r="D28" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1">
         <v>4.0</v>
       </c>
-      <c r="C29" s="4"/>
+      <c r="C29" s="3"/>
       <c r="D29" s="1">
         <v>3.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B30" s="1">
         <v>4.0</v>
       </c>
-      <c r="C30" s="4"/>
+      <c r="C30" s="3"/>
       <c r="D30" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B31" s="1">
         <v>4.0</v>
       </c>
-      <c r="C31" s="4"/>
+      <c r="C31" s="3"/>
       <c r="D31" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B32" s="1">
         <v>4.0</v>
       </c>
-      <c r="C32" s="4"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1">
         <v>4.0</v>
       </c>
-      <c r="C33" s="4"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B34" s="1">
         <v>4.0</v>
       </c>
-      <c r="C34" s="4"/>
+      <c r="C34" s="3"/>
       <c r="D34" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B35" s="1">
         <v>4.0</v>
       </c>
-      <c r="C35" s="4"/>
+      <c r="C35" s="3"/>
       <c r="D35" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B36" s="1">
         <v>4.0</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="3"/>
       <c r="D36" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1">
         <v>4.0</v>
       </c>
-      <c r="C37" s="4"/>
+      <c r="C37" s="3"/>
       <c r="D37" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B38" s="1">
         <v>4.0</v>
       </c>
-      <c r="C38" s="4"/>
+      <c r="C38" s="3"/>
       <c r="D38" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B39" s="1">
         <v>4.0</v>
       </c>
-      <c r="C39" s="4"/>
+      <c r="C39" s="3"/>
       <c r="D39" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C40" s="3"/>
       <c r="D40" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="B41" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C42" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C42" s="3"/>
       <c r="D42" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C43" s="3"/>
       <c r="D43" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C44" s="3"/>
       <c r="D44" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C45" s="3"/>
       <c r="D45" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="4"/>
+        <v>48</v>
+      </c>
+      <c r="B46" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="B47" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C47" s="3"/>
       <c r="D47" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="B48" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C48" s="3"/>
       <c r="D48" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" s="4"/>
+        <v>51</v>
+      </c>
+      <c r="B49" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C49" s="3"/>
       <c r="D49" s="1">
         <v>5.0</v>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="4"/>
+      <c r="A50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="51">
-      <c r="C51" s="4"/>
+      <c r="C51" s="3"/>
     </row>
     <row r="52">
-      <c r="C52" s="4"/>
+      <c r="C52" s="3"/>
     </row>
     <row r="53">
-      <c r="C53" s="4"/>
+      <c r="C53" s="3"/>
     </row>
     <row r="54">
-      <c r="C54" s="4"/>
+      <c r="C54" s="3"/>
     </row>
     <row r="55">
-      <c r="C55" s="4"/>
+      <c r="C55" s="3"/>
     </row>
     <row r="56">
-      <c r="C56" s="4"/>
+      <c r="C56" s="3"/>
     </row>
     <row r="57">
-      <c r="C57" s="4"/>
+      <c r="C57" s="3"/>
     </row>
     <row r="58">
-      <c r="C58" s="4"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59">
-      <c r="C59" s="4"/>
+      <c r="C59" s="3"/>
     </row>
     <row r="60">
-      <c r="C60" s="4"/>
+      <c r="C60" s="3"/>
     </row>
     <row r="61">
-      <c r="C61" s="4"/>
+      <c r="C61" s="3"/>
     </row>
     <row r="62">
-      <c r="C62" s="4"/>
+      <c r="C62" s="3"/>
     </row>
     <row r="63">
-      <c r="C63" s="4"/>
+      <c r="C63" s="3"/>
     </row>
     <row r="64">
-      <c r="C64" s="4"/>
+      <c r="C64" s="3"/>
     </row>
     <row r="65">
-      <c r="C65" s="4"/>
+      <c r="C65" s="3"/>
     </row>
     <row r="66">
-      <c r="C66" s="4"/>
+      <c r="C66" s="3"/>
     </row>
     <row r="67">
-      <c r="C67" s="4"/>
+      <c r="C67" s="3"/>
     </row>
     <row r="68">
-      <c r="C68" s="4"/>
+      <c r="C68" s="3"/>
     </row>
     <row r="69">
-      <c r="C69" s="4"/>
+      <c r="C69" s="3"/>
     </row>
     <row r="70">
-      <c r="C70" s="4"/>
+      <c r="C70" s="3"/>
     </row>
     <row r="71">
-      <c r="C71" s="4"/>
+      <c r="C71" s="3"/>
     </row>
     <row r="72">
-      <c r="C72" s="4"/>
+      <c r="C72" s="3"/>
     </row>
     <row r="73">
-      <c r="C73" s="4"/>
+      <c r="C73" s="3"/>
     </row>
     <row r="74">
-      <c r="C74" s="4"/>
+      <c r="C74" s="3"/>
     </row>
     <row r="75">
-      <c r="C75" s="4"/>
+      <c r="C75" s="3"/>
     </row>
     <row r="76">
-      <c r="C76" s="4"/>
+      <c r="C76" s="3"/>
     </row>
     <row r="77">
-      <c r="C77" s="4"/>
+      <c r="C77" s="3"/>
     </row>
     <row r="78">
-      <c r="C78" s="4"/>
+      <c r="C78" s="3"/>
     </row>
     <row r="79">
-      <c r="C79" s="4"/>
+      <c r="C79" s="3"/>
     </row>
     <row r="80">
-      <c r="C80" s="4"/>
+      <c r="C80" s="3"/>
     </row>
     <row r="81">
-      <c r="C81" s="4"/>
+      <c r="C81" s="3"/>
     </row>
     <row r="82">
-      <c r="C82" s="4"/>
+      <c r="C82" s="3"/>
     </row>
     <row r="83">
-      <c r="C83" s="4"/>
+      <c r="C83" s="3"/>
     </row>
     <row r="84">
-      <c r="C84" s="4"/>
+      <c r="C84" s="3"/>
     </row>
     <row r="85">
-      <c r="C85" s="4"/>
+      <c r="C85" s="3"/>
     </row>
     <row r="86">
-      <c r="C86" s="4"/>
+      <c r="C86" s="3"/>
     </row>
     <row r="87">
-      <c r="C87" s="4"/>
+      <c r="C87" s="3"/>
     </row>
     <row r="88">
-      <c r="C88" s="4"/>
+      <c r="C88" s="3"/>
     </row>
     <row r="89">
-      <c r="C89" s="4"/>
+      <c r="C89" s="3"/>
     </row>
     <row r="90">
-      <c r="C90" s="4"/>
+      <c r="C90" s="3"/>
     </row>
     <row r="91">
-      <c r="C91" s="4"/>
+      <c r="C91" s="3"/>
     </row>
     <row r="92">
-      <c r="C92" s="4"/>
+      <c r="C92" s="3"/>
     </row>
     <row r="93">
-      <c r="C93" s="4"/>
+      <c r="C93" s="3"/>
     </row>
     <row r="94">
-      <c r="C94" s="4"/>
+      <c r="C94" s="3"/>
     </row>
     <row r="95">
-      <c r="C95" s="4"/>
+      <c r="C95" s="3"/>
     </row>
     <row r="96">
-      <c r="C96" s="4"/>
+      <c r="C96" s="3"/>
     </row>
     <row r="97">
-      <c r="C97" s="4"/>
+      <c r="C97" s="3"/>
     </row>
     <row r="98">
-      <c r="C98" s="4"/>
+      <c r="C98" s="3"/>
     </row>
     <row r="99">
-      <c r="C99" s="4"/>
+      <c r="C99" s="3"/>
     </row>
     <row r="100">
-      <c r="C100" s="4"/>
+      <c r="C100" s="3"/>
     </row>
     <row r="101">
-      <c r="C101" s="4"/>
+      <c r="C101" s="3"/>
     </row>
     <row r="102">
-      <c r="C102" s="4"/>
+      <c r="C102" s="3"/>
     </row>
     <row r="103">
-      <c r="C103" s="4"/>
+      <c r="C103" s="3"/>
     </row>
     <row r="104">
-      <c r="C104" s="4"/>
+      <c r="C104" s="3"/>
     </row>
     <row r="105">
-      <c r="C105" s="4"/>
+      <c r="C105" s="3"/>
     </row>
     <row r="106">
-      <c r="C106" s="4"/>
+      <c r="C106" s="3"/>
     </row>
     <row r="107">
-      <c r="C107" s="4"/>
+      <c r="C107" s="3"/>
     </row>
     <row r="108">
-      <c r="C108" s="4"/>
+      <c r="C108" s="3"/>
     </row>
     <row r="109">
-      <c r="C109" s="4"/>
+      <c r="C109" s="3"/>
     </row>
     <row r="110">
-      <c r="C110" s="4"/>
+      <c r="C110" s="3"/>
     </row>
     <row r="111">
-      <c r="C111" s="4"/>
+      <c r="C111" s="3"/>
     </row>
     <row r="112">
-      <c r="C112" s="4"/>
+      <c r="C112" s="3"/>
     </row>
     <row r="113">
-      <c r="C113" s="4"/>
+      <c r="C113" s="3"/>
     </row>
     <row r="114">
-      <c r="C114" s="4"/>
+      <c r="C114" s="3"/>
     </row>
     <row r="115">
-      <c r="C115" s="4"/>
+      <c r="C115" s="3"/>
     </row>
     <row r="116">
-      <c r="C116" s="4"/>
+      <c r="C116" s="3"/>
     </row>
     <row r="117">
-      <c r="C117" s="4"/>
+      <c r="C117" s="3"/>
     </row>
     <row r="118">
-      <c r="C118" s="4"/>
+      <c r="C118" s="3"/>
     </row>
     <row r="119">
-      <c r="C119" s="4"/>
+      <c r="C119" s="3"/>
     </row>
     <row r="120">
-      <c r="C120" s="4"/>
+      <c r="C120" s="3"/>
     </row>
     <row r="121">
-      <c r="C121" s="4"/>
+      <c r="C121" s="3"/>
     </row>
     <row r="122">
-      <c r="C122" s="4"/>
+      <c r="C122" s="3"/>
     </row>
     <row r="123">
-      <c r="C123" s="4"/>
+      <c r="C123" s="3"/>
     </row>
     <row r="124">
-      <c r="C124" s="4"/>
+      <c r="C124" s="3"/>
     </row>
     <row r="125">
-      <c r="C125" s="4"/>
+      <c r="C125" s="3"/>
     </row>
     <row r="126">
-      <c r="C126" s="4"/>
+      <c r="C126" s="3"/>
     </row>
     <row r="127">
-      <c r="C127" s="4"/>
+      <c r="C127" s="3"/>
     </row>
     <row r="128">
-      <c r="C128" s="4"/>
+      <c r="C128" s="3"/>
     </row>
     <row r="129">
-      <c r="C129" s="4"/>
+      <c r="C129" s="3"/>
     </row>
     <row r="130">
-      <c r="C130" s="4"/>
+      <c r="C130" s="3"/>
     </row>
     <row r="131">
-      <c r="C131" s="4"/>
+      <c r="C131" s="3"/>
     </row>
     <row r="132">
-      <c r="C132" s="4"/>
+      <c r="C132" s="3"/>
     </row>
     <row r="133">
-      <c r="C133" s="4"/>
+      <c r="C133" s="3"/>
     </row>
     <row r="134">
-      <c r="C134" s="4"/>
+      <c r="C134" s="3"/>
     </row>
     <row r="135">
-      <c r="C135" s="4"/>
+      <c r="C135" s="3"/>
     </row>
     <row r="136">
-      <c r="C136" s="4"/>
+      <c r="C136" s="3"/>
     </row>
     <row r="137">
-      <c r="C137" s="4"/>
+      <c r="C137" s="3"/>
     </row>
     <row r="138">
-      <c r="C138" s="4"/>
+      <c r="C138" s="3"/>
     </row>
     <row r="139">
-      <c r="C139" s="4"/>
+      <c r="C139" s="3"/>
     </row>
     <row r="140">
-      <c r="C140" s="4"/>
+      <c r="C140" s="3"/>
     </row>
     <row r="141">
-      <c r="C141" s="4"/>
+      <c r="C141" s="3"/>
     </row>
     <row r="142">
-      <c r="C142" s="4"/>
+      <c r="C142" s="3"/>
     </row>
     <row r="143">
-      <c r="C143" s="4"/>
+      <c r="C143" s="3"/>
     </row>
     <row r="144">
-      <c r="C144" s="4"/>
+      <c r="C144" s="3"/>
     </row>
     <row r="145">
-      <c r="C145" s="4"/>
+      <c r="C145" s="3"/>
     </row>
     <row r="146">
-      <c r="C146" s="4"/>
+      <c r="C146" s="3"/>
     </row>
     <row r="147">
-      <c r="C147" s="4"/>
+      <c r="C147" s="3"/>
     </row>
     <row r="148">
-      <c r="C148" s="4"/>
+      <c r="C148" s="3"/>
     </row>
     <row r="149">
-      <c r="C149" s="4"/>
+      <c r="C149" s="3"/>
     </row>
     <row r="150">
-      <c r="C150" s="4"/>
+      <c r="C150" s="3"/>
     </row>
     <row r="151">
-      <c r="C151" s="4"/>
+      <c r="C151" s="3"/>
     </row>
     <row r="152">
-      <c r="C152" s="4"/>
+      <c r="C152" s="3"/>
     </row>
     <row r="153">
-      <c r="C153" s="4"/>
+      <c r="C153" s="3"/>
     </row>
     <row r="154">
-      <c r="C154" s="4"/>
+      <c r="C154" s="3"/>
     </row>
     <row r="155">
-      <c r="C155" s="4"/>
+      <c r="C155" s="3"/>
     </row>
     <row r="156">
-      <c r="C156" s="4"/>
+      <c r="C156" s="3"/>
     </row>
     <row r="157">
-      <c r="C157" s="4"/>
+      <c r="C157" s="3"/>
     </row>
     <row r="158">
-      <c r="C158" s="4"/>
+      <c r="C158" s="3"/>
     </row>
     <row r="159">
-      <c r="C159" s="4"/>
+      <c r="C159" s="3"/>
     </row>
     <row r="160">
-      <c r="C160" s="4"/>
+      <c r="C160" s="3"/>
     </row>
     <row r="161">
-      <c r="C161" s="4"/>
+      <c r="C161" s="3"/>
     </row>
     <row r="162">
-      <c r="C162" s="4"/>
+      <c r="C162" s="3"/>
     </row>
     <row r="163">
-      <c r="C163" s="4"/>
+      <c r="C163" s="3"/>
     </row>
     <row r="164">
-      <c r="C164" s="4"/>
+      <c r="C164" s="3"/>
     </row>
     <row r="165">
-      <c r="C165" s="4"/>
+      <c r="C165" s="3"/>
     </row>
     <row r="166">
-      <c r="C166" s="4"/>
+      <c r="C166" s="3"/>
     </row>
     <row r="167">
-      <c r="C167" s="4"/>
+      <c r="C167" s="3"/>
     </row>
     <row r="168">
-      <c r="C168" s="4"/>
+      <c r="C168" s="3"/>
     </row>
     <row r="169">
-      <c r="C169" s="4"/>
+      <c r="C169" s="3"/>
     </row>
     <row r="170">
-      <c r="C170" s="4"/>
+      <c r="C170" s="3"/>
     </row>
     <row r="171">
-      <c r="C171" s="4"/>
+      <c r="C171" s="3"/>
     </row>
     <row r="172">
-      <c r="C172" s="4"/>
+      <c r="C172" s="3"/>
     </row>
     <row r="173">
-      <c r="C173" s="4"/>
+      <c r="C173" s="3"/>
     </row>
     <row r="174">
-      <c r="C174" s="4"/>
+      <c r="C174" s="3"/>
     </row>
     <row r="175">
-      <c r="C175" s="4"/>
+      <c r="C175" s="3"/>
     </row>
     <row r="176">
-      <c r="C176" s="4"/>
+      <c r="C176" s="3"/>
     </row>
     <row r="177">
-      <c r="C177" s="4"/>
+      <c r="C177" s="3"/>
     </row>
     <row r="178">
-      <c r="C178" s="4"/>
+      <c r="C178" s="3"/>
     </row>
     <row r="179">
-      <c r="C179" s="4"/>
+      <c r="C179" s="3"/>
     </row>
     <row r="180">
-      <c r="C180" s="4"/>
+      <c r="C180" s="3"/>
     </row>
     <row r="181">
-      <c r="C181" s="4"/>
+      <c r="C181" s="3"/>
     </row>
     <row r="182">
-      <c r="C182" s="4"/>
+      <c r="C182" s="3"/>
     </row>
     <row r="183">
-      <c r="C183" s="4"/>
+      <c r="C183" s="3"/>
     </row>
     <row r="184">
-      <c r="C184" s="4"/>
+      <c r="C184" s="3"/>
     </row>
     <row r="185">
-      <c r="C185" s="4"/>
+      <c r="C185" s="3"/>
     </row>
     <row r="186">
-      <c r="C186" s="4"/>
+      <c r="C186" s="3"/>
     </row>
     <row r="187">
-      <c r="C187" s="4"/>
+      <c r="C187" s="3"/>
     </row>
     <row r="188">
-      <c r="C188" s="4"/>
+      <c r="C188" s="3"/>
     </row>
     <row r="189">
-      <c r="C189" s="4"/>
+      <c r="C189" s="3"/>
     </row>
     <row r="190">
-      <c r="C190" s="4"/>
+      <c r="C190" s="3"/>
     </row>
     <row r="191">
-      <c r="C191" s="4"/>
+      <c r="C191" s="3"/>
     </row>
     <row r="192">
-      <c r="C192" s="4"/>
+      <c r="C192" s="3"/>
     </row>
     <row r="193">
-      <c r="C193" s="4"/>
+      <c r="C193" s="3"/>
     </row>
     <row r="194">
-      <c r="C194" s="4"/>
+      <c r="C194" s="3"/>
     </row>
     <row r="195">
-      <c r="C195" s="4"/>
+      <c r="C195" s="3"/>
     </row>
     <row r="196">
-      <c r="C196" s="4"/>
+      <c r="C196" s="3"/>
     </row>
     <row r="197">
-      <c r="C197" s="4"/>
+      <c r="C197" s="3"/>
     </row>
     <row r="198">
-      <c r="C198" s="4"/>
+      <c r="C198" s="3"/>
     </row>
     <row r="199">
-      <c r="C199" s="4"/>
+      <c r="C199" s="3"/>
     </row>
     <row r="200">
-      <c r="C200" s="4"/>
+      <c r="C200" s="3"/>
     </row>
     <row r="201">
-      <c r="C201" s="4"/>
+      <c r="C201" s="3"/>
     </row>
     <row r="202">
-      <c r="C202" s="4"/>
+      <c r="C202" s="3"/>
     </row>
     <row r="203">
-      <c r="C203" s="4"/>
+      <c r="C203" s="3"/>
     </row>
     <row r="204">
-      <c r="C204" s="4"/>
+      <c r="C204" s="3"/>
     </row>
     <row r="205">
-      <c r="C205" s="4"/>
+      <c r="C205" s="3"/>
     </row>
     <row r="206">
-      <c r="C206" s="4"/>
+      <c r="C206" s="3"/>
     </row>
     <row r="207">
-      <c r="C207" s="4"/>
+      <c r="C207" s="3"/>
     </row>
     <row r="208">
-      <c r="C208" s="4"/>
+      <c r="C208" s="3"/>
     </row>
     <row r="209">
-      <c r="C209" s="4"/>
+      <c r="C209" s="3"/>
     </row>
     <row r="210">
-      <c r="C210" s="4"/>
+      <c r="C210" s="3"/>
     </row>
     <row r="211">
-      <c r="C211" s="4"/>
+      <c r="C211" s="3"/>
     </row>
     <row r="212">
-      <c r="C212" s="4"/>
+      <c r="C212" s="3"/>
     </row>
     <row r="213">
-      <c r="C213" s="4"/>
+      <c r="C213" s="3"/>
     </row>
     <row r="214">
-      <c r="C214" s="4"/>
+      <c r="C214" s="3"/>
     </row>
     <row r="215">
-      <c r="C215" s="4"/>
+      <c r="C215" s="3"/>
     </row>
     <row r="216">
-      <c r="C216" s="4"/>
+      <c r="C216" s="3"/>
     </row>
     <row r="217">
-      <c r="C217" s="4"/>
+      <c r="C217" s="3"/>
     </row>
     <row r="218">
-      <c r="C218" s="4"/>
+      <c r="C218" s="3"/>
     </row>
     <row r="219">
-      <c r="C219" s="4"/>
+      <c r="C219" s="3"/>
     </row>
     <row r="220">
-      <c r="C220" s="4"/>
+      <c r="C220" s="3"/>
     </row>
     <row r="221">
-      <c r="C221" s="4"/>
+      <c r="C221" s="3"/>
     </row>
     <row r="222">
-      <c r="C222" s="4"/>
+      <c r="C222" s="3"/>
     </row>
     <row r="223">
-      <c r="C223" s="4"/>
+      <c r="C223" s="3"/>
     </row>
     <row r="224">
-      <c r="C224" s="4"/>
+      <c r="C224" s="3"/>
     </row>
     <row r="225">
-      <c r="C225" s="4"/>
+      <c r="C225" s="3"/>
     </row>
     <row r="226">
-      <c r="C226" s="4"/>
+      <c r="C226" s="3"/>
     </row>
     <row r="227">
-      <c r="C227" s="4"/>
+      <c r="C227" s="3"/>
     </row>
     <row r="228">
-      <c r="C228" s="4"/>
+      <c r="C228" s="3"/>
     </row>
     <row r="229">
-      <c r="C229" s="4"/>
+      <c r="C229" s="3"/>
     </row>
     <row r="230">
-      <c r="C230" s="4"/>
+      <c r="C230" s="3"/>
     </row>
     <row r="231">
-      <c r="C231" s="4"/>
+      <c r="C231" s="3"/>
     </row>
     <row r="232">
-      <c r="C232" s="4"/>
+      <c r="C232" s="3"/>
     </row>
     <row r="233">
-      <c r="C233" s="4"/>
+      <c r="C233" s="3"/>
     </row>
     <row r="234">
-      <c r="C234" s="4"/>
+      <c r="C234" s="3"/>
     </row>
     <row r="235">
-      <c r="C235" s="4"/>
+      <c r="C235" s="3"/>
     </row>
     <row r="236">
-      <c r="C236" s="4"/>
+      <c r="C236" s="3"/>
     </row>
     <row r="237">
-      <c r="C237" s="4"/>
+      <c r="C237" s="3"/>
     </row>
     <row r="238">
-      <c r="C238" s="4"/>
+      <c r="C238" s="3"/>
     </row>
     <row r="239">
-      <c r="C239" s="4"/>
+      <c r="C239" s="3"/>
     </row>
     <row r="240">
-      <c r="C240" s="4"/>
+      <c r="C240" s="3"/>
     </row>
     <row r="241">
-      <c r="C241" s="4"/>
+      <c r="C241" s="3"/>
     </row>
     <row r="242">
-      <c r="C242" s="4"/>
+      <c r="C242" s="3"/>
     </row>
     <row r="243">
-      <c r="C243" s="4"/>
+      <c r="C243" s="3"/>
     </row>
     <row r="244">
-      <c r="C244" s="4"/>
+      <c r="C244" s="3"/>
     </row>
     <row r="245">
-      <c r="C245" s="4"/>
+      <c r="C245" s="3"/>
     </row>
     <row r="246">
-      <c r="C246" s="4"/>
+      <c r="C246" s="3"/>
     </row>
     <row r="247">
-      <c r="C247" s="4"/>
+      <c r="C247" s="3"/>
     </row>
     <row r="248">
-      <c r="C248" s="4"/>
+      <c r="C248" s="3"/>
     </row>
     <row r="249">
-      <c r="C249" s="4"/>
+      <c r="C249" s="3"/>
     </row>
     <row r="250">
-      <c r="C250" s="4"/>
+      <c r="C250" s="3"/>
     </row>
     <row r="251">
-      <c r="C251" s="4"/>
+      <c r="C251" s="3"/>
     </row>
     <row r="252">
-      <c r="C252" s="4"/>
+      <c r="C252" s="3"/>
     </row>
     <row r="253">
-      <c r="C253" s="4"/>
+      <c r="C253" s="3"/>
     </row>
     <row r="254">
-      <c r="C254" s="4"/>
+      <c r="C254" s="3"/>
     </row>
     <row r="255">
-      <c r="C255" s="4"/>
+      <c r="C255" s="3"/>
     </row>
     <row r="256">
-      <c r="C256" s="4"/>
+      <c r="C256" s="3"/>
     </row>
     <row r="257">
-      <c r="C257" s="4"/>
+      <c r="C257" s="3"/>
     </row>
     <row r="258">
-      <c r="C258" s="4"/>
+      <c r="C258" s="3"/>
     </row>
     <row r="259">
-      <c r="C259" s="4"/>
+      <c r="C259" s="3"/>
     </row>
     <row r="260">
-      <c r="C260" s="4"/>
+      <c r="C260" s="3"/>
     </row>
     <row r="261">
-      <c r="C261" s="4"/>
+      <c r="C261" s="3"/>
     </row>
     <row r="262">
-      <c r="C262" s="4"/>
+      <c r="C262" s="3"/>
     </row>
     <row r="263">
-      <c r="C263" s="4"/>
+      <c r="C263" s="3"/>
     </row>
     <row r="264">
-      <c r="C264" s="4"/>
+      <c r="C264" s="3"/>
     </row>
     <row r="265">
-      <c r="C265" s="4"/>
+      <c r="C265" s="3"/>
     </row>
     <row r="266">
-      <c r="C266" s="4"/>
+      <c r="C266" s="3"/>
     </row>
     <row r="267">
-      <c r="C267" s="4"/>
+      <c r="C267" s="3"/>
     </row>
     <row r="268">
-      <c r="C268" s="4"/>
+      <c r="C268" s="3"/>
     </row>
     <row r="269">
-      <c r="C269" s="4"/>
+      <c r="C269" s="3"/>
     </row>
     <row r="270">
-      <c r="C270" s="4"/>
+      <c r="C270" s="3"/>
     </row>
     <row r="271">
-      <c r="C271" s="4"/>
+      <c r="C271" s="3"/>
     </row>
     <row r="272">
-      <c r="C272" s="4"/>
+      <c r="C272" s="3"/>
     </row>
     <row r="273">
-      <c r="C273" s="4"/>
+      <c r="C273" s="3"/>
     </row>
     <row r="274">
-      <c r="C274" s="4"/>
+      <c r="C274" s="3"/>
     </row>
     <row r="275">
-      <c r="C275" s="4"/>
+      <c r="C275" s="3"/>
     </row>
     <row r="276">
-      <c r="C276" s="4"/>
+      <c r="C276" s="3"/>
     </row>
     <row r="277">
-      <c r="C277" s="4"/>
+      <c r="C277" s="3"/>
     </row>
     <row r="278">
-      <c r="C278" s="4"/>
+      <c r="C278" s="3"/>
     </row>
     <row r="279">
-      <c r="C279" s="4"/>
+      <c r="C279" s="3"/>
     </row>
     <row r="280">
-      <c r="C280" s="4"/>
+      <c r="C280" s="3"/>
     </row>
     <row r="281">
-      <c r="C281" s="4"/>
+      <c r="C281" s="3"/>
     </row>
     <row r="282">
-      <c r="C282" s="4"/>
+      <c r="C282" s="3"/>
     </row>
     <row r="283">
-      <c r="C283" s="4"/>
+      <c r="C283" s="3"/>
     </row>
     <row r="284">
-      <c r="C284" s="4"/>
+      <c r="C284" s="3"/>
     </row>
     <row r="285">
-      <c r="C285" s="4"/>
+      <c r="C285" s="3"/>
     </row>
     <row r="286">
-      <c r="C286" s="4"/>
+      <c r="C286" s="3"/>
     </row>
     <row r="287">
-      <c r="C287" s="4"/>
+      <c r="C287" s="3"/>
     </row>
     <row r="288">
-      <c r="C288" s="4"/>
+      <c r="C288" s="3"/>
     </row>
     <row r="289">
-      <c r="C289" s="4"/>
+      <c r="C289" s="3"/>
     </row>
     <row r="290">
-      <c r="C290" s="4"/>
+      <c r="C290" s="3"/>
     </row>
     <row r="291">
-      <c r="C291" s="4"/>
+      <c r="C291" s="3"/>
     </row>
     <row r="292">
-      <c r="C292" s="4"/>
+      <c r="C292" s="3"/>
     </row>
     <row r="293">
-      <c r="C293" s="4"/>
+      <c r="C293" s="3"/>
     </row>
     <row r="294">
-      <c r="C294" s="4"/>
+      <c r="C294" s="3"/>
     </row>
     <row r="295">
-      <c r="C295" s="4"/>
+      <c r="C295" s="3"/>
     </row>
     <row r="296">
-      <c r="C296" s="4"/>
+      <c r="C296" s="3"/>
     </row>
     <row r="297">
-      <c r="C297" s="4"/>
+      <c r="C297" s="3"/>
     </row>
     <row r="298">
-      <c r="C298" s="4"/>
+      <c r="C298" s="3"/>
     </row>
     <row r="299">
-      <c r="C299" s="4"/>
+      <c r="C299" s="3"/>
     </row>
     <row r="300">
-      <c r="C300" s="4"/>
+      <c r="C300" s="3"/>
     </row>
     <row r="301">
-      <c r="C301" s="4"/>
+      <c r="C301" s="3"/>
     </row>
     <row r="302">
-      <c r="C302" s="4"/>
+      <c r="C302" s="3"/>
     </row>
     <row r="303">
-      <c r="C303" s="4"/>
+      <c r="C303" s="3"/>
     </row>
     <row r="304">
-      <c r="C304" s="4"/>
+      <c r="C304" s="3"/>
     </row>
     <row r="305">
-      <c r="C305" s="4"/>
+      <c r="C305" s="3"/>
     </row>
     <row r="306">
-      <c r="C306" s="4"/>
+      <c r="C306" s="3"/>
     </row>
     <row r="307">
-      <c r="C307" s="4"/>
+      <c r="C307" s="3"/>
     </row>
     <row r="308">
-      <c r="C308" s="4"/>
+      <c r="C308" s="3"/>
     </row>
     <row r="309">
-      <c r="C309" s="4"/>
+      <c r="C309" s="3"/>
     </row>
     <row r="310">
-      <c r="C310" s="4"/>
+      <c r="C310" s="3"/>
     </row>
     <row r="311">
-      <c r="C311" s="4"/>
+      <c r="C311" s="3"/>
     </row>
     <row r="312">
-      <c r="C312" s="4"/>
+      <c r="C312" s="3"/>
     </row>
     <row r="313">
-      <c r="C313" s="4"/>
+      <c r="C313" s="3"/>
     </row>
     <row r="314">
-      <c r="C314" s="4"/>
+      <c r="C314" s="3"/>
     </row>
     <row r="315">
-      <c r="C315" s="4"/>
+      <c r="C315" s="3"/>
     </row>
     <row r="316">
-      <c r="C316" s="4"/>
+      <c r="C316" s="3"/>
     </row>
     <row r="317">
-      <c r="C317" s="4"/>
+      <c r="C317" s="3"/>
     </row>
     <row r="318">
-      <c r="C318" s="4"/>
+      <c r="C318" s="3"/>
     </row>
     <row r="319">
-      <c r="C319" s="4"/>
+      <c r="C319" s="3"/>
     </row>
     <row r="320">
-      <c r="C320" s="4"/>
+      <c r="C320" s="3"/>
     </row>
     <row r="321">
-      <c r="C321" s="4"/>
+      <c r="C321" s="3"/>
     </row>
     <row r="322">
-      <c r="C322" s="4"/>
+      <c r="C322" s="3"/>
     </row>
     <row r="323">
-      <c r="C323" s="4"/>
+      <c r="C323" s="3"/>
     </row>
     <row r="324">
-      <c r="C324" s="4"/>
+      <c r="C324" s="3"/>
     </row>
     <row r="325">
-      <c r="C325" s="4"/>
+      <c r="C325" s="3"/>
     </row>
     <row r="326">
-      <c r="C326" s="4"/>
+      <c r="C326" s="3"/>
     </row>
     <row r="327">
-      <c r="C327" s="4"/>
+      <c r="C327" s="3"/>
     </row>
     <row r="328">
-      <c r="C328" s="4"/>
+      <c r="C328" s="3"/>
     </row>
     <row r="329">
-      <c r="C329" s="4"/>
+      <c r="C329" s="3"/>
     </row>
     <row r="330">
-      <c r="C330" s="4"/>
+      <c r="C330" s="3"/>
     </row>
     <row r="331">
-      <c r="C331" s="4"/>
+      <c r="C331" s="3"/>
     </row>
     <row r="332">
-      <c r="C332" s="4"/>
+      <c r="C332" s="3"/>
     </row>
     <row r="333">
-      <c r="C333" s="4"/>
+      <c r="C333" s="3"/>
     </row>
     <row r="334">
-      <c r="C334" s="4"/>
+      <c r="C334" s="3"/>
     </row>
     <row r="335">
-      <c r="C335" s="4"/>
+      <c r="C335" s="3"/>
     </row>
     <row r="336">
-      <c r="C336" s="4"/>
+      <c r="C336" s="3"/>
     </row>
     <row r="337">
-      <c r="C337" s="4"/>
+      <c r="C337" s="3"/>
     </row>
     <row r="338">
-      <c r="C338" s="4"/>
+      <c r="C338" s="3"/>
     </row>
     <row r="339">
-      <c r="C339" s="4"/>
+      <c r="C339" s="3"/>
     </row>
     <row r="340">
-      <c r="C340" s="4"/>
+      <c r="C340" s="3"/>
     </row>
     <row r="341">
-      <c r="C341" s="4"/>
+      <c r="C341" s="3"/>
     </row>
     <row r="342">
-      <c r="C342" s="4"/>
+      <c r="C342" s="3"/>
     </row>
     <row r="343">
-      <c r="C343" s="4"/>
+      <c r="C343" s="3"/>
     </row>
     <row r="344">
-      <c r="C344" s="4"/>
+      <c r="C344" s="3"/>
     </row>
     <row r="345">
-      <c r="C345" s="4"/>
+      <c r="C345" s="3"/>
     </row>
     <row r="346">
-      <c r="C346" s="4"/>
+      <c r="C346" s="3"/>
     </row>
     <row r="347">
-      <c r="C347" s="4"/>
+      <c r="C347" s="3"/>
     </row>
     <row r="348">
-      <c r="C348" s="4"/>
+      <c r="C348" s="3"/>
     </row>
     <row r="349">
-      <c r="C349" s="4"/>
+      <c r="C349" s="3"/>
     </row>
     <row r="350">
-      <c r="C350" s="4"/>
+      <c r="C350" s="3"/>
     </row>
     <row r="351">
-      <c r="C351" s="4"/>
+      <c r="C351" s="3"/>
     </row>
     <row r="352">
-      <c r="C352" s="4"/>
+      <c r="C352" s="3"/>
     </row>
     <row r="353">
-      <c r="C353" s="4"/>
+      <c r="C353" s="3"/>
     </row>
     <row r="354">
-      <c r="C354" s="4"/>
+      <c r="C354" s="3"/>
     </row>
     <row r="355">
-      <c r="C355" s="4"/>
+      <c r="C355" s="3"/>
     </row>
     <row r="356">
-      <c r="C356" s="4"/>
+      <c r="C356" s="3"/>
     </row>
     <row r="357">
-      <c r="C357" s="4"/>
+      <c r="C357" s="3"/>
     </row>
     <row r="358">
-      <c r="C358" s="4"/>
+      <c r="C358" s="3"/>
     </row>
     <row r="359">
-      <c r="C359" s="4"/>
+      <c r="C359" s="3"/>
     </row>
     <row r="360">
-      <c r="C360" s="4"/>
+      <c r="C360" s="3"/>
     </row>
     <row r="361">
-      <c r="C361" s="4"/>
+      <c r="C361" s="3"/>
     </row>
     <row r="362">
-      <c r="C362" s="4"/>
+      <c r="C362" s="3"/>
     </row>
     <row r="363">
-      <c r="C363" s="4"/>
+      <c r="C363" s="3"/>
     </row>
     <row r="364">
-      <c r="C364" s="4"/>
+      <c r="C364" s="3"/>
     </row>
     <row r="365">
-      <c r="C365" s="4"/>
+      <c r="C365" s="3"/>
     </row>
     <row r="366">
-      <c r="C366" s="4"/>
+      <c r="C366" s="3"/>
     </row>
     <row r="367">
-      <c r="C367" s="4"/>
+      <c r="C367" s="3"/>
     </row>
     <row r="368">
-      <c r="C368" s="4"/>
+      <c r="C368" s="3"/>
     </row>
     <row r="369">
-      <c r="C369" s="4"/>
+      <c r="C369" s="3"/>
     </row>
     <row r="370">
-      <c r="C370" s="4"/>
+      <c r="C370" s="3"/>
     </row>
     <row r="371">
-      <c r="C371" s="4"/>
+      <c r="C371" s="3"/>
     </row>
     <row r="372">
-      <c r="C372" s="4"/>
+      <c r="C372" s="3"/>
     </row>
     <row r="373">
-      <c r="C373" s="4"/>
+      <c r="C373" s="3"/>
     </row>
     <row r="374">
-      <c r="C374" s="4"/>
+      <c r="C374" s="3"/>
     </row>
     <row r="375">
-      <c r="C375" s="4"/>
+      <c r="C375" s="3"/>
     </row>
     <row r="376">
-      <c r="C376" s="4"/>
+      <c r="C376" s="3"/>
     </row>
     <row r="377">
-      <c r="C377" s="4"/>
+      <c r="C377" s="3"/>
     </row>
     <row r="378">
-      <c r="C378" s="4"/>
+      <c r="C378" s="3"/>
     </row>
     <row r="379">
-      <c r="C379" s="4"/>
+      <c r="C379" s="3"/>
     </row>
     <row r="380">
-      <c r="C380" s="4"/>
+      <c r="C380" s="3"/>
     </row>
     <row r="381">
-      <c r="C381" s="4"/>
+      <c r="C381" s="3"/>
     </row>
     <row r="382">
-      <c r="C382" s="4"/>
+      <c r="C382" s="3"/>
     </row>
     <row r="383">
-      <c r="C383" s="4"/>
+      <c r="C383" s="3"/>
     </row>
     <row r="384">
-      <c r="C384" s="4"/>
+      <c r="C384" s="3"/>
     </row>
     <row r="385">
-      <c r="C385" s="4"/>
+      <c r="C385" s="3"/>
     </row>
     <row r="386">
-      <c r="C386" s="4"/>
+      <c r="C386" s="3"/>
     </row>
     <row r="387">
-      <c r="C387" s="4"/>
+      <c r="C387" s="3"/>
     </row>
     <row r="388">
-      <c r="C388" s="4"/>
+      <c r="C388" s="3"/>
     </row>
     <row r="389">
-      <c r="C389" s="4"/>
+      <c r="C389" s="3"/>
     </row>
     <row r="390">
-      <c r="C390" s="4"/>
+      <c r="C390" s="3"/>
     </row>
     <row r="391">
-      <c r="C391" s="4"/>
+      <c r="C391" s="3"/>
     </row>
     <row r="392">
-      <c r="C392" s="4"/>
+      <c r="C392" s="3"/>
     </row>
     <row r="393">
-      <c r="C393" s="4"/>
+      <c r="C393" s="3"/>
     </row>
     <row r="394">
-      <c r="C394" s="4"/>
+      <c r="C394" s="3"/>
     </row>
     <row r="395">
-      <c r="C395" s="4"/>
+      <c r="C395" s="3"/>
     </row>
     <row r="396">
-      <c r="C396" s="4"/>
+      <c r="C396" s="3"/>
     </row>
     <row r="397">
-      <c r="C397" s="4"/>
+      <c r="C397" s="3"/>
     </row>
     <row r="398">
-      <c r="C398" s="4"/>
+      <c r="C398" s="3"/>
     </row>
     <row r="399">
-      <c r="C399" s="4"/>
+      <c r="C399" s="3"/>
     </row>
     <row r="400">
-      <c r="C400" s="4"/>
+      <c r="C400" s="3"/>
     </row>
     <row r="401">
-      <c r="C401" s="4"/>
+      <c r="C401" s="3"/>
     </row>
     <row r="402">
-      <c r="C402" s="4"/>
+      <c r="C402" s="3"/>
     </row>
     <row r="403">
-      <c r="C403" s="4"/>
+      <c r="C403" s="3"/>
     </row>
     <row r="404">
-      <c r="C404" s="4"/>
+      <c r="C404" s="3"/>
     </row>
     <row r="405">
-      <c r="C405" s="4"/>
+      <c r="C405" s="3"/>
     </row>
     <row r="406">
-      <c r="C406" s="4"/>
+      <c r="C406" s="3"/>
     </row>
     <row r="407">
-      <c r="C407" s="4"/>
+      <c r="C407" s="3"/>
     </row>
     <row r="408">
-      <c r="C408" s="4"/>
+      <c r="C408" s="3"/>
     </row>
     <row r="409">
-      <c r="C409" s="4"/>
+      <c r="C409" s="3"/>
     </row>
     <row r="410">
-      <c r="C410" s="4"/>
+      <c r="C410" s="3"/>
     </row>
     <row r="411">
-      <c r="C411" s="4"/>
+      <c r="C411" s="3"/>
     </row>
     <row r="412">
-      <c r="C412" s="4"/>
+      <c r="C412" s="3"/>
     </row>
     <row r="413">
-      <c r="C413" s="4"/>
+      <c r="C413" s="3"/>
     </row>
     <row r="414">
-      <c r="C414" s="4"/>
+      <c r="C414" s="3"/>
     </row>
     <row r="415">
-      <c r="C415" s="4"/>
+      <c r="C415" s="3"/>
     </row>
     <row r="416">
-      <c r="C416" s="4"/>
+      <c r="C416" s="3"/>
     </row>
     <row r="417">
-      <c r="C417" s="4"/>
+      <c r="C417" s="3"/>
     </row>
     <row r="418">
-      <c r="C418" s="4"/>
+      <c r="C418" s="3"/>
     </row>
     <row r="419">
-      <c r="C419" s="4"/>
+      <c r="C419" s="3"/>
     </row>
     <row r="420">
-      <c r="C420" s="4"/>
+      <c r="C420" s="3"/>
     </row>
     <row r="421">
-      <c r="C421" s="4"/>
+      <c r="C421" s="3"/>
     </row>
     <row r="422">
-      <c r="C422" s="4"/>
+      <c r="C422" s="3"/>
     </row>
     <row r="423">
-      <c r="C423" s="4"/>
+      <c r="C423" s="3"/>
     </row>
     <row r="424">
-      <c r="C424" s="4"/>
+      <c r="C424" s="3"/>
     </row>
     <row r="425">
-      <c r="C425" s="4"/>
+      <c r="C425" s="3"/>
     </row>
     <row r="426">
-      <c r="C426" s="4"/>
+      <c r="C426" s="3"/>
     </row>
     <row r="427">
-      <c r="C427" s="4"/>
+      <c r="C427" s="3"/>
     </row>
     <row r="428">
-      <c r="C428" s="4"/>
+      <c r="C428" s="3"/>
     </row>
     <row r="429">
-      <c r="C429" s="4"/>
+      <c r="C429" s="3"/>
     </row>
     <row r="430">
-      <c r="C430" s="4"/>
+      <c r="C430" s="3"/>
     </row>
     <row r="431">
-      <c r="C431" s="4"/>
+      <c r="C431" s="3"/>
     </row>
     <row r="432">
-      <c r="C432" s="4"/>
+      <c r="C432" s="3"/>
     </row>
     <row r="433">
-      <c r="C433" s="4"/>
+      <c r="C433" s="3"/>
     </row>
     <row r="434">
-      <c r="C434" s="4"/>
+      <c r="C434" s="3"/>
     </row>
     <row r="435">
-      <c r="C435" s="4"/>
+      <c r="C435" s="3"/>
     </row>
     <row r="436">
-      <c r="C436" s="4"/>
+      <c r="C436" s="3"/>
     </row>
     <row r="437">
-      <c r="C437" s="4"/>
+      <c r="C437" s="3"/>
     </row>
     <row r="438">
-      <c r="C438" s="4"/>
+      <c r="C438" s="3"/>
     </row>
     <row r="439">
-      <c r="C439" s="4"/>
+      <c r="C439" s="3"/>
     </row>
     <row r="440">
-      <c r="C440" s="4"/>
+      <c r="C440" s="3"/>
     </row>
     <row r="441">
-      <c r="C441" s="4"/>
+      <c r="C441" s="3"/>
     </row>
     <row r="442">
-      <c r="C442" s="4"/>
+      <c r="C442" s="3"/>
     </row>
     <row r="443">
-      <c r="C443" s="4"/>
+      <c r="C443" s="3"/>
     </row>
     <row r="444">
-      <c r="C444" s="4"/>
+      <c r="C444" s="3"/>
     </row>
     <row r="445">
-      <c r="C445" s="4"/>
+      <c r="C445" s="3"/>
     </row>
     <row r="446">
-      <c r="C446" s="4"/>
+      <c r="C446" s="3"/>
     </row>
     <row r="447">
-      <c r="C447" s="4"/>
+      <c r="C447" s="3"/>
     </row>
     <row r="448">
-      <c r="C448" s="4"/>
+      <c r="C448" s="3"/>
     </row>
     <row r="449">
-      <c r="C449" s="4"/>
+      <c r="C449" s="3"/>
     </row>
     <row r="450">
-      <c r="C450" s="4"/>
+      <c r="C450" s="3"/>
     </row>
     <row r="451">
-      <c r="C451" s="4"/>
+      <c r="C451" s="3"/>
     </row>
     <row r="452">
-      <c r="C452" s="4"/>
+      <c r="C452" s="3"/>
     </row>
     <row r="453">
-      <c r="C453" s="4"/>
+      <c r="C453" s="3"/>
     </row>
     <row r="454">
-      <c r="C454" s="4"/>
+      <c r="C454" s="3"/>
     </row>
     <row r="455">
-      <c r="C455" s="4"/>
+      <c r="C455" s="3"/>
     </row>
     <row r="456">
-      <c r="C456" s="4"/>
+      <c r="C456" s="3"/>
     </row>
     <row r="457">
-      <c r="C457" s="4"/>
+      <c r="C457" s="3"/>
     </row>
     <row r="458">
-      <c r="C458" s="4"/>
+      <c r="C458" s="3"/>
     </row>
     <row r="459">
-      <c r="C459" s="4"/>
+      <c r="C459" s="3"/>
     </row>
     <row r="460">
-      <c r="C460" s="4"/>
+      <c r="C460" s="3"/>
     </row>
     <row r="461">
-      <c r="C461" s="4"/>
+      <c r="C461" s="3"/>
     </row>
     <row r="462">
-      <c r="C462" s="4"/>
+      <c r="C462" s="3"/>
     </row>
     <row r="463">
-      <c r="C463" s="4"/>
+      <c r="C463" s="3"/>
     </row>
     <row r="464">
-      <c r="C464" s="4"/>
+      <c r="C464" s="3"/>
     </row>
     <row r="465">
-      <c r="C465" s="4"/>
+      <c r="C465" s="3"/>
     </row>
     <row r="466">
-      <c r="C466" s="4"/>
+      <c r="C466" s="3"/>
     </row>
     <row r="467">
-      <c r="C467" s="4"/>
+      <c r="C467" s="3"/>
     </row>
     <row r="468">
-      <c r="C468" s="4"/>
+      <c r="C468" s="3"/>
     </row>
     <row r="469">
-      <c r="C469" s="4"/>
+      <c r="C469" s="3"/>
     </row>
     <row r="470">
-      <c r="C470" s="4"/>
+      <c r="C470" s="3"/>
     </row>
     <row r="471">
-      <c r="C471" s="4"/>
+      <c r="C471" s="3"/>
     </row>
     <row r="472">
-      <c r="C472" s="4"/>
+      <c r="C472" s="3"/>
     </row>
     <row r="473">
-      <c r="C473" s="4"/>
+      <c r="C473" s="3"/>
     </row>
     <row r="474">
-      <c r="C474" s="4"/>
+      <c r="C474" s="3"/>
     </row>
     <row r="475">
-      <c r="C475" s="4"/>
+      <c r="C475" s="3"/>
     </row>
     <row r="476">
-      <c r="C476" s="4"/>
+      <c r="C476" s="3"/>
     </row>
     <row r="477">
-      <c r="C477" s="4"/>
+      <c r="C477" s="3"/>
     </row>
     <row r="478">
-      <c r="C478" s="4"/>
+      <c r="C478" s="3"/>
     </row>
     <row r="479">
-      <c r="C479" s="4"/>
+      <c r="C479" s="3"/>
     </row>
     <row r="480">
-      <c r="C480" s="4"/>
+      <c r="C480" s="3"/>
     </row>
     <row r="481">
-      <c r="C481" s="4"/>
+      <c r="C481" s="3"/>
     </row>
     <row r="482">
-      <c r="C482" s="4"/>
+      <c r="C482" s="3"/>
     </row>
     <row r="483">
-      <c r="C483" s="4"/>
+      <c r="C483" s="3"/>
     </row>
     <row r="484">
-      <c r="C484" s="4"/>
+      <c r="C484" s="3"/>
     </row>
     <row r="485">
-      <c r="C485" s="4"/>
+      <c r="C485" s="3"/>
     </row>
     <row r="486">
-      <c r="C486" s="4"/>
+      <c r="C486" s="3"/>
     </row>
     <row r="487">
-      <c r="C487" s="4"/>
+      <c r="C487" s="3"/>
     </row>
     <row r="488">
-      <c r="C488" s="4"/>
+      <c r="C488" s="3"/>
     </row>
     <row r="489">
-      <c r="C489" s="4"/>
+      <c r="C489" s="3"/>
     </row>
     <row r="490">
-      <c r="C490" s="4"/>
+      <c r="C490" s="3"/>
     </row>
     <row r="491">
-      <c r="C491" s="4"/>
+      <c r="C491" s="3"/>
     </row>
     <row r="492">
-      <c r="C492" s="4"/>
+      <c r="C492" s="3"/>
     </row>
     <row r="493">
-      <c r="C493" s="4"/>
+      <c r="C493" s="3"/>
     </row>
     <row r="494">
-      <c r="C494" s="4"/>
+      <c r="C494" s="3"/>
     </row>
     <row r="495">
-      <c r="C495" s="4"/>
+      <c r="C495" s="3"/>
     </row>
     <row r="496">
-      <c r="C496" s="4"/>
+      <c r="C496" s="3"/>
     </row>
     <row r="497">
-      <c r="C497" s="4"/>
+      <c r="C497" s="3"/>
     </row>
     <row r="498">
-      <c r="C498" s="4"/>
+      <c r="C498" s="3"/>
     </row>
     <row r="499">
-      <c r="C499" s="4"/>
+      <c r="C499" s="3"/>
     </row>
     <row r="500">
-      <c r="C500" s="4"/>
+      <c r="C500" s="3"/>
     </row>
     <row r="501">
-      <c r="C501" s="4"/>
+      <c r="C501" s="3"/>
     </row>
     <row r="502">
-      <c r="C502" s="4"/>
+      <c r="C502" s="3"/>
     </row>
     <row r="503">
-      <c r="C503" s="4"/>
+      <c r="C503" s="3"/>
     </row>
     <row r="504">
-      <c r="C504" s="4"/>
+      <c r="C504" s="3"/>
     </row>
     <row r="505">
-      <c r="C505" s="4"/>
+      <c r="C505" s="3"/>
     </row>
     <row r="506">
-      <c r="C506" s="4"/>
+      <c r="C506" s="3"/>
     </row>
     <row r="507">
-      <c r="C507" s="4"/>
+      <c r="C507" s="3"/>
     </row>
     <row r="508">
-      <c r="C508" s="4"/>
+      <c r="C508" s="3"/>
     </row>
     <row r="509">
-      <c r="C509" s="4"/>
+      <c r="C509" s="3"/>
     </row>
     <row r="510">
-      <c r="C510" s="4"/>
+      <c r="C510" s="3"/>
     </row>
     <row r="511">
-      <c r="C511" s="4"/>
+      <c r="C511" s="3"/>
     </row>
     <row r="512">
-      <c r="C512" s="4"/>
+      <c r="C512" s="3"/>
     </row>
     <row r="513">
-      <c r="C513" s="4"/>
+      <c r="C513" s="3"/>
     </row>
     <row r="514">
-      <c r="C514" s="4"/>
+      <c r="C514" s="3"/>
     </row>
     <row r="515">
-      <c r="C515" s="4"/>
+      <c r="C515" s="3"/>
     </row>
     <row r="516">
-      <c r="C516" s="4"/>
+      <c r="C516" s="3"/>
     </row>
     <row r="517">
-      <c r="C517" s="4"/>
+      <c r="C517" s="3"/>
     </row>
     <row r="518">
-      <c r="C518" s="4"/>
+      <c r="C518" s="3"/>
     </row>
     <row r="519">
-      <c r="C519" s="4"/>
+      <c r="C519" s="3"/>
     </row>
     <row r="520">
-      <c r="C520" s="4"/>
+      <c r="C520" s="3"/>
     </row>
     <row r="521">
-      <c r="C521" s="4"/>
+      <c r="C521" s="3"/>
     </row>
     <row r="522">
-      <c r="C522" s="4"/>
+      <c r="C522" s="3"/>
     </row>
     <row r="523">
-      <c r="C523" s="4"/>
+      <c r="C523" s="3"/>
     </row>
     <row r="524">
-      <c r="C524" s="4"/>
+      <c r="C524" s="3"/>
     </row>
     <row r="525">
-      <c r="C525" s="4"/>
+      <c r="C525" s="3"/>
     </row>
     <row r="526">
-      <c r="C526" s="4"/>
+      <c r="C526" s="3"/>
     </row>
     <row r="527">
-      <c r="C527" s="4"/>
+      <c r="C527" s="3"/>
     </row>
     <row r="528">
-      <c r="C528" s="4"/>
+      <c r="C528" s="3"/>
     </row>
     <row r="529">
-      <c r="C529" s="4"/>
+      <c r="C529" s="3"/>
     </row>
     <row r="530">
-      <c r="C530" s="4"/>
+      <c r="C530" s="3"/>
     </row>
     <row r="531">
-      <c r="C531" s="4"/>
+      <c r="C531" s="3"/>
     </row>
     <row r="532">
-      <c r="C532" s="4"/>
+      <c r="C532" s="3"/>
     </row>
     <row r="533">
-      <c r="C533" s="4"/>
+      <c r="C533" s="3"/>
     </row>
     <row r="534">
-      <c r="C534" s="4"/>
+      <c r="C534" s="3"/>
     </row>
     <row r="535">
-      <c r="C535" s="4"/>
+      <c r="C535" s="3"/>
     </row>
     <row r="536">
-      <c r="C536" s="4"/>
+      <c r="C536" s="3"/>
     </row>
     <row r="537">
-      <c r="C537" s="4"/>
+      <c r="C537" s="3"/>
     </row>
     <row r="538">
-      <c r="C538" s="4"/>
+      <c r="C538" s="3"/>
     </row>
     <row r="539">
-      <c r="C539" s="4"/>
+      <c r="C539" s="3"/>
     </row>
     <row r="540">
-      <c r="C540" s="4"/>
+      <c r="C540" s="3"/>
     </row>
     <row r="541">
-      <c r="C541" s="4"/>
+      <c r="C541" s="3"/>
     </row>
     <row r="542">
-      <c r="C542" s="4"/>
+      <c r="C542" s="3"/>
     </row>
     <row r="543">
-      <c r="C543" s="4"/>
+      <c r="C543" s="3"/>
     </row>
     <row r="544">
-      <c r="C544" s="4"/>
+      <c r="C544" s="3"/>
     </row>
     <row r="545">
-      <c r="C545" s="4"/>
+      <c r="C545" s="3"/>
     </row>
     <row r="546">
-      <c r="C546" s="4"/>
+      <c r="C546" s="3"/>
     </row>
     <row r="547">
-      <c r="C547" s="4"/>
+      <c r="C547" s="3"/>
     </row>
     <row r="548">
-      <c r="C548" s="4"/>
+      <c r="C548" s="3"/>
     </row>
     <row r="549">
-      <c r="C549" s="4"/>
+      <c r="C549" s="3"/>
     </row>
     <row r="550">
-      <c r="C550" s="4"/>
+      <c r="C550" s="3"/>
     </row>
     <row r="551">
-      <c r="C551" s="4"/>
+      <c r="C551" s="3"/>
     </row>
     <row r="552">
-      <c r="C552" s="4"/>
+      <c r="C552" s="3"/>
     </row>
     <row r="553">
-      <c r="C553" s="4"/>
+      <c r="C553" s="3"/>
     </row>
     <row r="554">
-      <c r="C554" s="4"/>
+      <c r="C554" s="3"/>
     </row>
     <row r="555">
-      <c r="C555" s="4"/>
+      <c r="C555" s="3"/>
     </row>
     <row r="556">
-      <c r="C556" s="4"/>
+      <c r="C556" s="3"/>
     </row>
     <row r="557">
-      <c r="C557" s="4"/>
+      <c r="C557" s="3"/>
     </row>
     <row r="558">
-      <c r="C558" s="4"/>
+      <c r="C558" s="3"/>
     </row>
     <row r="559">
-      <c r="C559" s="4"/>
+      <c r="C559" s="3"/>
     </row>
     <row r="560">
-      <c r="C560" s="4"/>
+      <c r="C560" s="3"/>
     </row>
     <row r="561">
-      <c r="C561" s="4"/>
+      <c r="C561" s="3"/>
     </row>
     <row r="562">
-      <c r="C562" s="4"/>
+      <c r="C562" s="3"/>
     </row>
     <row r="563">
-      <c r="C563" s="4"/>
+      <c r="C563" s="3"/>
     </row>
     <row r="564">
-      <c r="C564" s="4"/>
+      <c r="C564" s="3"/>
     </row>
     <row r="565">
-      <c r="C565" s="4"/>
+      <c r="C565" s="3"/>
     </row>
     <row r="566">
-      <c r="C566" s="4"/>
+      <c r="C566" s="3"/>
     </row>
     <row r="567">
-      <c r="C567" s="4"/>
+      <c r="C567" s="3"/>
     </row>
     <row r="568">
-      <c r="C568" s="4"/>
+      <c r="C568" s="3"/>
     </row>
     <row r="569">
-      <c r="C569" s="4"/>
+      <c r="C569" s="3"/>
     </row>
     <row r="570">
-      <c r="C570" s="4"/>
+      <c r="C570" s="3"/>
     </row>
     <row r="571">
-      <c r="C571" s="4"/>
+      <c r="C571" s="3"/>
     </row>
     <row r="572">
-      <c r="C572" s="4"/>
+      <c r="C572" s="3"/>
     </row>
     <row r="573">
-      <c r="C573" s="4"/>
+      <c r="C573" s="3"/>
     </row>
     <row r="574">
-      <c r="C574" s="4"/>
+      <c r="C574" s="3"/>
     </row>
     <row r="575">
-      <c r="C575" s="4"/>
+      <c r="C575" s="3"/>
     </row>
     <row r="576">
-      <c r="C576" s="4"/>
+      <c r="C576" s="3"/>
     </row>
     <row r="577">
-      <c r="C577" s="4"/>
+      <c r="C577" s="3"/>
     </row>
     <row r="578">
-      <c r="C578" s="4"/>
+      <c r="C578" s="3"/>
     </row>
     <row r="579">
-      <c r="C579" s="4"/>
+      <c r="C579" s="3"/>
     </row>
     <row r="580">
-      <c r="C580" s="4"/>
+      <c r="C580" s="3"/>
     </row>
     <row r="581">
-      <c r="C581" s="4"/>
+      <c r="C581" s="3"/>
     </row>
     <row r="582">
-      <c r="C582" s="4"/>
+      <c r="C582" s="3"/>
     </row>
     <row r="583">
-      <c r="C583" s="4"/>
+      <c r="C583" s="3"/>
     </row>
     <row r="584">
-      <c r="C584" s="4"/>
+      <c r="C584" s="3"/>
     </row>
     <row r="585">
-      <c r="C585" s="4"/>
+      <c r="C585" s="3"/>
     </row>
     <row r="586">
-      <c r="C586" s="4"/>
+      <c r="C586" s="3"/>
     </row>
     <row r="587">
-      <c r="C587" s="4"/>
+      <c r="C587" s="3"/>
     </row>
     <row r="588">
-      <c r="C588" s="4"/>
+      <c r="C588" s="3"/>
     </row>
     <row r="589">
-      <c r="C589" s="4"/>
+      <c r="C589" s="3"/>
     </row>
     <row r="590">
-      <c r="C590" s="4"/>
+      <c r="C590" s="3"/>
     </row>
     <row r="591">
-      <c r="C591" s="4"/>
+      <c r="C591" s="3"/>
     </row>
     <row r="592">
-      <c r="C592" s="4"/>
+      <c r="C592" s="3"/>
     </row>
     <row r="593">
-      <c r="C593" s="4"/>
+      <c r="C593" s="3"/>
     </row>
     <row r="594">
-      <c r="C594" s="4"/>
+      <c r="C594" s="3"/>
     </row>
     <row r="595">
-      <c r="C595" s="4"/>
+      <c r="C595" s="3"/>
     </row>
     <row r="596">
-      <c r="C596" s="4"/>
+      <c r="C596" s="3"/>
     </row>
     <row r="597">
-      <c r="C597" s="4"/>
+      <c r="C597" s="3"/>
     </row>
     <row r="598">
-      <c r="C598" s="4"/>
+      <c r="C598" s="3"/>
     </row>
     <row r="599">
-      <c r="C599" s="4"/>
+      <c r="C599" s="3"/>
     </row>
     <row r="600">
-      <c r="C600" s="4"/>
+      <c r="C600" s="3"/>
     </row>
     <row r="601">
-      <c r="C601" s="4"/>
+      <c r="C601" s="3"/>
     </row>
     <row r="602">
-      <c r="C602" s="4"/>
+      <c r="C602" s="3"/>
     </row>
     <row r="603">
-      <c r="C603" s="4"/>
+      <c r="C603" s="3"/>
     </row>
     <row r="604">
-      <c r="C604" s="4"/>
+      <c r="C604" s="3"/>
     </row>
     <row r="605">
-      <c r="C605" s="4"/>
+      <c r="C605" s="3"/>
     </row>
     <row r="606">
-      <c r="C606" s="4"/>
+      <c r="C606" s="3"/>
     </row>
     <row r="607">
-      <c r="C607" s="4"/>
+      <c r="C607" s="3"/>
     </row>
     <row r="608">
-      <c r="C608" s="4"/>
+      <c r="C608" s="3"/>
     </row>
     <row r="609">
-      <c r="C609" s="4"/>
+      <c r="C609" s="3"/>
     </row>
     <row r="610">
-      <c r="C610" s="4"/>
+      <c r="C610" s="3"/>
     </row>
     <row r="611">
-      <c r="C611" s="4"/>
+      <c r="C611" s="3"/>
     </row>
     <row r="612">
-      <c r="C612" s="4"/>
+      <c r="C612" s="3"/>
     </row>
     <row r="613">
-      <c r="C613" s="4"/>
+      <c r="C613" s="3"/>
     </row>
     <row r="614">
-      <c r="C614" s="4"/>
+      <c r="C614" s="3"/>
     </row>
     <row r="615">
-      <c r="C615" s="4"/>
+      <c r="C615" s="3"/>
     </row>
     <row r="616">
-      <c r="C616" s="4"/>
+      <c r="C616" s="3"/>
     </row>
     <row r="617">
-      <c r="C617" s="4"/>
+      <c r="C617" s="3"/>
     </row>
     <row r="618">
-      <c r="C618" s="4"/>
+      <c r="C618" s="3"/>
     </row>
     <row r="619">
-      <c r="C619" s="4"/>
+      <c r="C619" s="3"/>
     </row>
     <row r="620">
-      <c r="C620" s="4"/>
+      <c r="C620" s="3"/>
     </row>
     <row r="621">
-      <c r="C621" s="4"/>
+      <c r="C621" s="3"/>
     </row>
     <row r="622">
-      <c r="C622" s="4"/>
+      <c r="C622" s="3"/>
     </row>
     <row r="623">
-      <c r="C623" s="4"/>
+      <c r="C623" s="3"/>
     </row>
     <row r="624">
-      <c r="C624" s="4"/>
+      <c r="C624" s="3"/>
     </row>
     <row r="625">
-      <c r="C625" s="4"/>
+      <c r="C625" s="3"/>
     </row>
     <row r="626">
-      <c r="C626" s="4"/>
+      <c r="C626" s="3"/>
     </row>
     <row r="627">
-      <c r="C627" s="4"/>
+      <c r="C627" s="3"/>
     </row>
     <row r="628">
-      <c r="C628" s="4"/>
+      <c r="C628" s="3"/>
     </row>
     <row r="629">
-      <c r="C629" s="4"/>
+      <c r="C629" s="3"/>
     </row>
     <row r="630">
-      <c r="C630" s="4"/>
+      <c r="C630" s="3"/>
     </row>
     <row r="631">
-      <c r="C631" s="4"/>
+      <c r="C631" s="3"/>
     </row>
     <row r="632">
-      <c r="C632" s="4"/>
+      <c r="C632" s="3"/>
     </row>
     <row r="633">
-      <c r="C633" s="4"/>
+      <c r="C633" s="3"/>
     </row>
     <row r="634">
-      <c r="C634" s="4"/>
+      <c r="C634" s="3"/>
     </row>
     <row r="635">
-      <c r="C635" s="4"/>
+      <c r="C635" s="3"/>
     </row>
     <row r="636">
-      <c r="C636" s="4"/>
+      <c r="C636" s="3"/>
     </row>
     <row r="637">
-      <c r="C637" s="4"/>
+      <c r="C637" s="3"/>
     </row>
     <row r="638">
-      <c r="C638" s="4"/>
+      <c r="C638" s="3"/>
     </row>
     <row r="639">
-      <c r="C639" s="4"/>
+      <c r="C639" s="3"/>
     </row>
     <row r="640">
-      <c r="C640" s="4"/>
+      <c r="C640" s="3"/>
     </row>
     <row r="641">
-      <c r="C641" s="4"/>
+      <c r="C641" s="3"/>
     </row>
     <row r="642">
-      <c r="C642" s="4"/>
+      <c r="C642" s="3"/>
     </row>
     <row r="643">
-      <c r="C643" s="4"/>
+      <c r="C643" s="3"/>
     </row>
     <row r="644">
-      <c r="C644" s="4"/>
+      <c r="C644" s="3"/>
     </row>
     <row r="645">
-      <c r="C645" s="4"/>
+      <c r="C645" s="3"/>
     </row>
     <row r="646">
-      <c r="C646" s="4"/>
+      <c r="C646" s="3"/>
     </row>
     <row r="647">
-      <c r="C647" s="4"/>
+      <c r="C647" s="3"/>
     </row>
     <row r="648">
-      <c r="C648" s="4"/>
+      <c r="C648" s="3"/>
     </row>
     <row r="649">
-      <c r="C649" s="4"/>
+      <c r="C649" s="3"/>
     </row>
     <row r="650">
-      <c r="C650" s="4"/>
+      <c r="C650" s="3"/>
     </row>
     <row r="651">
-      <c r="C651" s="4"/>
+      <c r="C651" s="3"/>
     </row>
     <row r="652">
-      <c r="C652" s="4"/>
+      <c r="C652" s="3"/>
     </row>
     <row r="653">
-      <c r="C653" s="4"/>
+      <c r="C653" s="3"/>
     </row>
     <row r="654">
-      <c r="C654" s="4"/>
+      <c r="C654" s="3"/>
     </row>
     <row r="655">
-      <c r="C655" s="4"/>
+      <c r="C655" s="3"/>
     </row>
     <row r="656">
-      <c r="C656" s="4"/>
+      <c r="C656" s="3"/>
     </row>
     <row r="657">
-      <c r="C657" s="4"/>
+      <c r="C657" s="3"/>
     </row>
     <row r="658">
-      <c r="C658" s="4"/>
+      <c r="C658" s="3"/>
     </row>
     <row r="659">
-      <c r="C659" s="4"/>
+      <c r="C659" s="3"/>
     </row>
     <row r="660">
-      <c r="C660" s="4"/>
+      <c r="C660" s="3"/>
     </row>
     <row r="661">
-      <c r="C661" s="4"/>
+      <c r="C661" s="3"/>
     </row>
     <row r="662">
-      <c r="C662" s="4"/>
+      <c r="C662" s="3"/>
     </row>
     <row r="663">
-      <c r="C663" s="4"/>
+      <c r="C663" s="3"/>
     </row>
     <row r="664">
-      <c r="C664" s="4"/>
+      <c r="C664" s="3"/>
     </row>
     <row r="665">
-      <c r="C665" s="4"/>
+      <c r="C665" s="3"/>
     </row>
     <row r="666">
-      <c r="C666" s="4"/>
+      <c r="C666" s="3"/>
     </row>
     <row r="667">
-      <c r="C667" s="4"/>
+      <c r="C667" s="3"/>
     </row>
     <row r="668">
-      <c r="C668" s="4"/>
+      <c r="C668" s="3"/>
     </row>
     <row r="669">
-      <c r="C669" s="4"/>
+      <c r="C669" s="3"/>
     </row>
     <row r="670">
-      <c r="C670" s="4"/>
+      <c r="C670" s="3"/>
     </row>
     <row r="671">
-      <c r="C671" s="4"/>
+      <c r="C671" s="3"/>
     </row>
     <row r="672">
-      <c r="C672" s="4"/>
+      <c r="C672" s="3"/>
     </row>
     <row r="673">
-      <c r="C673" s="4"/>
+      <c r="C673" s="3"/>
     </row>
     <row r="674">
-      <c r="C674" s="4"/>
+      <c r="C674" s="3"/>
     </row>
     <row r="675">
-      <c r="C675" s="4"/>
+      <c r="C675" s="3"/>
     </row>
     <row r="676">
-      <c r="C676" s="4"/>
+      <c r="C676" s="3"/>
     </row>
     <row r="677">
-      <c r="C677" s="4"/>
+      <c r="C677" s="3"/>
     </row>
     <row r="678">
-      <c r="C678" s="4"/>
+      <c r="C678" s="3"/>
     </row>
     <row r="679">
-      <c r="C679" s="4"/>
+      <c r="C679" s="3"/>
     </row>
     <row r="680">
-      <c r="C680" s="4"/>
+      <c r="C680" s="3"/>
     </row>
     <row r="681">
-      <c r="C681" s="4"/>
+      <c r="C681" s="3"/>
     </row>
     <row r="682">
-      <c r="C682" s="4"/>
+      <c r="C682" s="3"/>
     </row>
     <row r="683">
-      <c r="C683" s="4"/>
+      <c r="C683" s="3"/>
     </row>
     <row r="684">
-      <c r="C684" s="4"/>
+      <c r="C684" s="3"/>
     </row>
     <row r="685">
-      <c r="C685" s="4"/>
+      <c r="C685" s="3"/>
     </row>
     <row r="686">
-      <c r="C686" s="4"/>
+      <c r="C686" s="3"/>
     </row>
     <row r="687">
-      <c r="C687" s="4"/>
+      <c r="C687" s="3"/>
     </row>
     <row r="688">
-      <c r="C688" s="4"/>
+      <c r="C688" s="3"/>
     </row>
     <row r="689">
-      <c r="C689" s="4"/>
+      <c r="C689" s="3"/>
     </row>
     <row r="690">
-      <c r="C690" s="4"/>
+      <c r="C690" s="3"/>
     </row>
     <row r="691">
-      <c r="C691" s="4"/>
+      <c r="C691" s="3"/>
     </row>
     <row r="692">
-      <c r="C692" s="4"/>
+      <c r="C692" s="3"/>
     </row>
     <row r="693">
-      <c r="C693" s="4"/>
+      <c r="C693" s="3"/>
     </row>
     <row r="694">
-      <c r="C694" s="4"/>
+      <c r="C694" s="3"/>
     </row>
     <row r="695">
-      <c r="C695" s="4"/>
+      <c r="C695" s="3"/>
     </row>
     <row r="696">
-      <c r="C696" s="4"/>
+      <c r="C696" s="3"/>
     </row>
     <row r="697">
-      <c r="C697" s="4"/>
+      <c r="C697" s="3"/>
     </row>
     <row r="698">
-      <c r="C698" s="4"/>
+      <c r="C698" s="3"/>
     </row>
     <row r="699">
-      <c r="C699" s="4"/>
+      <c r="C699" s="3"/>
     </row>
     <row r="700">
-      <c r="C700" s="4"/>
+      <c r="C700" s="3"/>
     </row>
     <row r="701">
-      <c r="C701" s="4"/>
+      <c r="C701" s="3"/>
     </row>
     <row r="702">
-      <c r="C702" s="4"/>
+      <c r="C702" s="3"/>
     </row>
     <row r="703">
-      <c r="C703" s="4"/>
+      <c r="C703" s="3"/>
     </row>
     <row r="704">
-      <c r="C704" s="4"/>
+      <c r="C704" s="3"/>
     </row>
     <row r="705">
-      <c r="C705" s="4"/>
+      <c r="C705" s="3"/>
     </row>
     <row r="706">
-      <c r="C706" s="4"/>
+      <c r="C706" s="3"/>
     </row>
     <row r="707">
-      <c r="C707" s="4"/>
+      <c r="C707" s="3"/>
     </row>
     <row r="708">
-      <c r="C708" s="4"/>
+      <c r="C708" s="3"/>
     </row>
     <row r="709">
-      <c r="C709" s="4"/>
+      <c r="C709" s="3"/>
     </row>
     <row r="710">
-      <c r="C710" s="4"/>
+      <c r="C710" s="3"/>
     </row>
     <row r="711">
-      <c r="C711" s="4"/>
+      <c r="C711" s="3"/>
     </row>
     <row r="712">
-      <c r="C712" s="4"/>
+      <c r="C712" s="3"/>
     </row>
     <row r="713">
-      <c r="C713" s="4"/>
+      <c r="C713" s="3"/>
     </row>
     <row r="714">
-      <c r="C714" s="4"/>
+      <c r="C714" s="3"/>
     </row>
     <row r="715">
-      <c r="C715" s="4"/>
+      <c r="C715" s="3"/>
     </row>
     <row r="716">
-      <c r="C716" s="4"/>
+      <c r="C716" s="3"/>
     </row>
     <row r="717">
-      <c r="C717" s="4"/>
+      <c r="C717" s="3"/>
     </row>
     <row r="718">
-      <c r="C718" s="4"/>
+      <c r="C718" s="3"/>
     </row>
     <row r="719">
-      <c r="C719" s="4"/>
+      <c r="C719" s="3"/>
     </row>
     <row r="720">
-      <c r="C720" s="4"/>
+      <c r="C720" s="3"/>
     </row>
     <row r="721">
-      <c r="C721" s="4"/>
+      <c r="C721" s="3"/>
     </row>
     <row r="722">
-      <c r="C722" s="4"/>
+      <c r="C722" s="3"/>
     </row>
     <row r="723">
-      <c r="C723" s="4"/>
+      <c r="C723" s="3"/>
     </row>
     <row r="724">
-      <c r="C724" s="4"/>
+      <c r="C724" s="3"/>
     </row>
     <row r="725">
-      <c r="C725" s="4"/>
+      <c r="C725" s="3"/>
     </row>
     <row r="726">
-      <c r="C726" s="4"/>
+      <c r="C726" s="3"/>
     </row>
     <row r="727">
-      <c r="C727" s="4"/>
+      <c r="C727" s="3"/>
     </row>
     <row r="728">
-      <c r="C728" s="4"/>
+      <c r="C728" s="3"/>
     </row>
     <row r="729">
-      <c r="C729" s="4"/>
+      <c r="C729" s="3"/>
     </row>
     <row r="730">
-      <c r="C730" s="4"/>
+      <c r="C730" s="3"/>
     </row>
     <row r="731">
-      <c r="C731" s="4"/>
+      <c r="C731" s="3"/>
     </row>
     <row r="732">
-      <c r="C732" s="4"/>
+      <c r="C732" s="3"/>
     </row>
     <row r="733">
-      <c r="C733" s="4"/>
+      <c r="C733" s="3"/>
     </row>
     <row r="734">
-      <c r="C734" s="4"/>
+      <c r="C734" s="3"/>
     </row>
     <row r="735">
-      <c r="C735" s="4"/>
+      <c r="C735" s="3"/>
     </row>
     <row r="736">
-      <c r="C736" s="4"/>
+      <c r="C736" s="3"/>
     </row>
     <row r="737">
-      <c r="C737" s="4"/>
+      <c r="C737" s="3"/>
     </row>
     <row r="738">
-      <c r="C738" s="4"/>
+      <c r="C738" s="3"/>
     </row>
     <row r="739">
-      <c r="C739" s="4"/>
+      <c r="C739" s="3"/>
     </row>
     <row r="740">
-      <c r="C740" s="4"/>
+      <c r="C740" s="3"/>
     </row>
     <row r="741">
-      <c r="C741" s="4"/>
+      <c r="C741" s="3"/>
     </row>
     <row r="742">
-      <c r="C742" s="4"/>
+      <c r="C742" s="3"/>
     </row>
     <row r="743">
-      <c r="C743" s="4"/>
+      <c r="C743" s="3"/>
     </row>
     <row r="744">
-      <c r="C744" s="4"/>
+      <c r="C744" s="3"/>
     </row>
     <row r="745">
-      <c r="C745" s="4"/>
+      <c r="C745" s="3"/>
     </row>
     <row r="746">
-      <c r="C746" s="4"/>
+      <c r="C746" s="3"/>
     </row>
     <row r="747">
-      <c r="C747" s="4"/>
+      <c r="C747" s="3"/>
     </row>
     <row r="748">
-      <c r="C748" s="4"/>
+      <c r="C748" s="3"/>
     </row>
     <row r="749">
-      <c r="C749" s="4"/>
+      <c r="C749" s="3"/>
     </row>
     <row r="750">
-      <c r="C750" s="4"/>
+      <c r="C750" s="3"/>
     </row>
     <row r="751">
-      <c r="C751" s="4"/>
+      <c r="C751" s="3"/>
     </row>
     <row r="752">
-      <c r="C752" s="4"/>
+      <c r="C752" s="3"/>
     </row>
     <row r="753">
-      <c r="C753" s="4"/>
+      <c r="C753" s="3"/>
     </row>
     <row r="754">
-      <c r="C754" s="4"/>
+      <c r="C754" s="3"/>
     </row>
     <row r="755">
-      <c r="C755" s="4"/>
+      <c r="C755" s="3"/>
     </row>
     <row r="756">
-      <c r="C756" s="4"/>
+      <c r="C756" s="3"/>
     </row>
     <row r="757">
-      <c r="C757" s="4"/>
+      <c r="C757" s="3"/>
     </row>
     <row r="758">
-      <c r="C758" s="4"/>
+      <c r="C758" s="3"/>
     </row>
     <row r="759">
-      <c r="C759" s="4"/>
+      <c r="C759" s="3"/>
     </row>
     <row r="760">
-      <c r="C760" s="4"/>
+      <c r="C760" s="3"/>
     </row>
     <row r="761">
-      <c r="C761" s="4"/>
+      <c r="C761" s="3"/>
     </row>
     <row r="762">
-      <c r="C762" s="4"/>
+      <c r="C762" s="3"/>
     </row>
     <row r="763">
-      <c r="C763" s="4"/>
+      <c r="C763" s="3"/>
     </row>
     <row r="764">
-      <c r="C764" s="4"/>
+      <c r="C764" s="3"/>
     </row>
     <row r="765">
-      <c r="C765" s="4"/>
+      <c r="C765" s="3"/>
     </row>
     <row r="766">
-      <c r="C766" s="4"/>
+      <c r="C766" s="3"/>
     </row>
     <row r="767">
-      <c r="C767" s="4"/>
+      <c r="C767" s="3"/>
     </row>
     <row r="768">
-      <c r="C768" s="4"/>
+      <c r="C768" s="3"/>
     </row>
     <row r="769">
-      <c r="C769" s="4"/>
+      <c r="C769" s="3"/>
     </row>
     <row r="770">
-      <c r="C770" s="4"/>
+      <c r="C770" s="3"/>
     </row>
     <row r="771">
-      <c r="C771" s="4"/>
+      <c r="C771" s="3"/>
     </row>
     <row r="772">
-      <c r="C772" s="4"/>
+      <c r="C772" s="3"/>
     </row>
     <row r="773">
-      <c r="C773" s="4"/>
+      <c r="C773" s="3"/>
     </row>
     <row r="774">
-      <c r="C774" s="4"/>
+      <c r="C774" s="3"/>
     </row>
     <row r="775">
-      <c r="C775" s="4"/>
+      <c r="C775" s="3"/>
     </row>
     <row r="776">
-      <c r="C776" s="4"/>
+      <c r="C776" s="3"/>
     </row>
     <row r="777">
-      <c r="C777" s="4"/>
+      <c r="C777" s="3"/>
     </row>
     <row r="778">
-      <c r="C778" s="4"/>
+      <c r="C778" s="3"/>
     </row>
     <row r="779">
-      <c r="C779" s="4"/>
+      <c r="C779" s="3"/>
     </row>
     <row r="780">
-      <c r="C780" s="4"/>
+      <c r="C780" s="3"/>
     </row>
     <row r="781">
-      <c r="C781" s="4"/>
+      <c r="C781" s="3"/>
     </row>
     <row r="782">
-      <c r="C782" s="4"/>
+      <c r="C782" s="3"/>
     </row>
     <row r="783">
-      <c r="C783" s="4"/>
+      <c r="C783" s="3"/>
     </row>
     <row r="784">
-      <c r="C784" s="4"/>
+      <c r="C784" s="3"/>
     </row>
     <row r="785">
-      <c r="C785" s="4"/>
+      <c r="C785" s="3"/>
     </row>
     <row r="786">
-      <c r="C786" s="4"/>
+      <c r="C786" s="3"/>
     </row>
     <row r="787">
-      <c r="C787" s="4"/>
+      <c r="C787" s="3"/>
     </row>
     <row r="788">
-      <c r="C788" s="4"/>
+      <c r="C788" s="3"/>
     </row>
     <row r="789">
-      <c r="C789" s="4"/>
+      <c r="C789" s="3"/>
     </row>
     <row r="790">
-      <c r="C790" s="4"/>
+      <c r="C790" s="3"/>
     </row>
     <row r="791">
-      <c r="C791" s="4"/>
+      <c r="C791" s="3"/>
     </row>
     <row r="792">
-      <c r="C792" s="4"/>
+      <c r="C792" s="3"/>
     </row>
     <row r="793">
-      <c r="C793" s="4"/>
+      <c r="C793" s="3"/>
     </row>
     <row r="794">
-      <c r="C794" s="4"/>
+      <c r="C794" s="3"/>
     </row>
     <row r="795">
-      <c r="C795" s="4"/>
+      <c r="C795" s="3"/>
     </row>
     <row r="796">
-      <c r="C796" s="4"/>
+      <c r="C796" s="3"/>
     </row>
     <row r="797">
-      <c r="C797" s="4"/>
+      <c r="C797" s="3"/>
     </row>
     <row r="798">
-      <c r="C798" s="4"/>
+      <c r="C798" s="3"/>
     </row>
     <row r="799">
-      <c r="C799" s="4"/>
+      <c r="C799" s="3"/>
     </row>
     <row r="800">
-      <c r="C800" s="4"/>
+      <c r="C800" s="3"/>
     </row>
     <row r="801">
-      <c r="C801" s="4"/>
+      <c r="C801" s="3"/>
     </row>
     <row r="802">
-      <c r="C802" s="4"/>
+      <c r="C802" s="3"/>
     </row>
     <row r="803">
-      <c r="C803" s="4"/>
+      <c r="C803" s="3"/>
     </row>
     <row r="804">
-      <c r="C804" s="4"/>
+      <c r="C804" s="3"/>
     </row>
     <row r="805">
-      <c r="C805" s="4"/>
+      <c r="C805" s="3"/>
     </row>
     <row r="806">
-      <c r="C806" s="4"/>
+      <c r="C806" s="3"/>
     </row>
     <row r="807">
-      <c r="C807" s="4"/>
+      <c r="C807" s="3"/>
     </row>
     <row r="808">
-      <c r="C808" s="4"/>
+      <c r="C808" s="3"/>
     </row>
     <row r="809">
-      <c r="C809" s="4"/>
+      <c r="C809" s="3"/>
     </row>
     <row r="810">
-      <c r="C810" s="4"/>
+      <c r="C810" s="3"/>
     </row>
     <row r="811">
-      <c r="C811" s="4"/>
+      <c r="C811" s="3"/>
     </row>
     <row r="812">
-      <c r="C812" s="4"/>
+      <c r="C812" s="3"/>
     </row>
     <row r="813">
-      <c r="C813" s="4"/>
+      <c r="C813" s="3"/>
     </row>
     <row r="814">
-      <c r="C814" s="4"/>
+      <c r="C814" s="3"/>
     </row>
     <row r="815">
-      <c r="C815" s="4"/>
+      <c r="C815" s="3"/>
     </row>
     <row r="816">
-      <c r="C816" s="4"/>
+      <c r="C816" s="3"/>
     </row>
     <row r="817">
-      <c r="C817" s="4"/>
+      <c r="C817" s="3"/>
     </row>
     <row r="818">
-      <c r="C818" s="4"/>
+      <c r="C818" s="3"/>
     </row>
     <row r="819">
-      <c r="C819" s="4"/>
+      <c r="C819" s="3"/>
     </row>
     <row r="820">
-      <c r="C820" s="4"/>
+      <c r="C820" s="3"/>
     </row>
     <row r="821">
-      <c r="C821" s="4"/>
+      <c r="C821" s="3"/>
     </row>
     <row r="822">
-      <c r="C822" s="4"/>
+      <c r="C822" s="3"/>
     </row>
     <row r="823">
-      <c r="C823" s="4"/>
+      <c r="C823" s="3"/>
     </row>
     <row r="824">
-      <c r="C824" s="4"/>
+      <c r="C824" s="3"/>
     </row>
     <row r="825">
-      <c r="C825" s="4"/>
+      <c r="C825" s="3"/>
     </row>
     <row r="826">
-      <c r="C826" s="4"/>
+      <c r="C826" s="3"/>
     </row>
     <row r="827">
-      <c r="C827" s="4"/>
+      <c r="C827" s="3"/>
     </row>
     <row r="828">
-      <c r="C828" s="4"/>
+      <c r="C828" s="3"/>
     </row>
     <row r="829">
-      <c r="C829" s="4"/>
+      <c r="C829" s="3"/>
     </row>
     <row r="830">
-      <c r="C830" s="4"/>
+      <c r="C830" s="3"/>
     </row>
     <row r="831">
-      <c r="C831" s="4"/>
+      <c r="C831" s="3"/>
     </row>
     <row r="832">
-      <c r="C832" s="4"/>
+      <c r="C832" s="3"/>
     </row>
     <row r="833">
-      <c r="C833" s="4"/>
+      <c r="C833" s="3"/>
     </row>
     <row r="834">
-      <c r="C834" s="4"/>
+      <c r="C834" s="3"/>
     </row>
     <row r="835">
-      <c r="C835" s="4"/>
+      <c r="C835" s="3"/>
     </row>
     <row r="836">
-      <c r="C836" s="4"/>
+      <c r="C836" s="3"/>
     </row>
     <row r="837">
-      <c r="C837" s="4"/>
+      <c r="C837" s="3"/>
     </row>
     <row r="838">
-      <c r="C838" s="4"/>
+      <c r="C838" s="3"/>
     </row>
     <row r="839">
-      <c r="C839" s="4"/>
+      <c r="C839" s="3"/>
     </row>
     <row r="840">
-      <c r="C840" s="4"/>
+      <c r="C840" s="3"/>
     </row>
     <row r="841">
-      <c r="C841" s="4"/>
+      <c r="C841" s="3"/>
     </row>
     <row r="842">
-      <c r="C842" s="4"/>
+      <c r="C842" s="3"/>
     </row>
     <row r="843">
-      <c r="C843" s="4"/>
+      <c r="C843" s="3"/>
     </row>
     <row r="844">
-      <c r="C844" s="4"/>
+      <c r="C844" s="3"/>
     </row>
     <row r="845">
-      <c r="C845" s="4"/>
+      <c r="C845" s="3"/>
     </row>
     <row r="846">
-      <c r="C846" s="4"/>
+      <c r="C846" s="3"/>
     </row>
     <row r="847">
-      <c r="C847" s="4"/>
+      <c r="C847" s="3"/>
     </row>
     <row r="848">
-      <c r="C848" s="4"/>
+      <c r="C848" s="3"/>
     </row>
     <row r="849">
-      <c r="C849" s="4"/>
+      <c r="C849" s="3"/>
     </row>
     <row r="850">
-      <c r="C850" s="4"/>
+      <c r="C850" s="3"/>
     </row>
     <row r="851">
-      <c r="C851" s="4"/>
+      <c r="C851" s="3"/>
     </row>
     <row r="852">
-      <c r="C852" s="4"/>
+      <c r="C852" s="3"/>
     </row>
     <row r="853">
-      <c r="C853" s="4"/>
+      <c r="C853" s="3"/>
     </row>
     <row r="854">
-      <c r="C854" s="4"/>
+      <c r="C854" s="3"/>
     </row>
     <row r="855">
-      <c r="C855" s="4"/>
+      <c r="C855" s="3"/>
     </row>
     <row r="856">
-      <c r="C856" s="4"/>
+      <c r="C856" s="3"/>
     </row>
     <row r="857">
-      <c r="C857" s="4"/>
+      <c r="C857" s="3"/>
     </row>
     <row r="858">
-      <c r="C858" s="4"/>
+      <c r="C858" s="3"/>
     </row>
     <row r="859">
-      <c r="C859" s="4"/>
+      <c r="C859" s="3"/>
     </row>
     <row r="860">
-      <c r="C860" s="4"/>
+      <c r="C860" s="3"/>
     </row>
     <row r="861">
-      <c r="C861" s="4"/>
+      <c r="C861" s="3"/>
     </row>
     <row r="862">
-      <c r="C862" s="4"/>
+      <c r="C862" s="3"/>
     </row>
     <row r="863">
-      <c r="C863" s="4"/>
+      <c r="C863" s="3"/>
     </row>
     <row r="864">
-      <c r="C864" s="4"/>
+      <c r="C864" s="3"/>
     </row>
     <row r="865">
-      <c r="C865" s="4"/>
+      <c r="C865" s="3"/>
     </row>
     <row r="866">
-      <c r="C866" s="4"/>
+      <c r="C866" s="3"/>
     </row>
     <row r="867">
-      <c r="C867" s="4"/>
+      <c r="C867" s="3"/>
     </row>
     <row r="868">
-      <c r="C868" s="4"/>
+      <c r="C868" s="3"/>
     </row>
     <row r="869">
-      <c r="C869" s="4"/>
+      <c r="C869" s="3"/>
     </row>
     <row r="870">
-      <c r="C870" s="4"/>
+      <c r="C870" s="3"/>
     </row>
     <row r="871">
-      <c r="C871" s="4"/>
+      <c r="C871" s="3"/>
     </row>
     <row r="872">
-      <c r="C872" s="4"/>
+      <c r="C872" s="3"/>
     </row>
     <row r="873">
-      <c r="C873" s="4"/>
+      <c r="C873" s="3"/>
     </row>
     <row r="874">
-      <c r="C874" s="4"/>
+      <c r="C874" s="3"/>
     </row>
     <row r="875">
-      <c r="C875" s="4"/>
+      <c r="C875" s="3"/>
     </row>
     <row r="876">
-      <c r="C876" s="4"/>
+      <c r="C876" s="3"/>
     </row>
     <row r="877">
-      <c r="C877" s="4"/>
+      <c r="C877" s="3"/>
     </row>
     <row r="878">
-      <c r="C878" s="4"/>
+      <c r="C878" s="3"/>
     </row>
     <row r="879">
-      <c r="C879" s="4"/>
+      <c r="C879" s="3"/>
     </row>
     <row r="880">
-      <c r="C880" s="4"/>
+      <c r="C880" s="3"/>
     </row>
     <row r="881">
-      <c r="C881" s="4"/>
+      <c r="C881" s="3"/>
     </row>
     <row r="882">
-      <c r="C882" s="4"/>
+      <c r="C882" s="3"/>
     </row>
     <row r="883">
-      <c r="C883" s="4"/>
+      <c r="C883" s="3"/>
     </row>
     <row r="884">
-      <c r="C884" s="4"/>
+      <c r="C884" s="3"/>
     </row>
     <row r="885">
-      <c r="C885" s="4"/>
+      <c r="C885" s="3"/>
     </row>
     <row r="886">
-      <c r="C886" s="4"/>
+      <c r="C886" s="3"/>
     </row>
     <row r="887">
-      <c r="C887" s="4"/>
+      <c r="C887" s="3"/>
     </row>
     <row r="888">
-      <c r="C888" s="4"/>
+      <c r="C888" s="3"/>
     </row>
     <row r="889">
-      <c r="C889" s="4"/>
+      <c r="C889" s="3"/>
     </row>
     <row r="890">
-      <c r="C890" s="4"/>
+      <c r="C890" s="3"/>
     </row>
     <row r="891">
-      <c r="C891" s="4"/>
+      <c r="C891" s="3"/>
     </row>
     <row r="892">
-      <c r="C892" s="4"/>
+      <c r="C892" s="3"/>
     </row>
     <row r="893">
-      <c r="C893" s="4"/>
+      <c r="C893" s="3"/>
     </row>
     <row r="894">
-      <c r="C894" s="4"/>
+      <c r="C894" s="3"/>
     </row>
     <row r="895">
-      <c r="C895" s="4"/>
+      <c r="C895" s="3"/>
     </row>
     <row r="896">
-      <c r="C896" s="4"/>
+      <c r="C896" s="3"/>
     </row>
     <row r="897">
-      <c r="C897" s="4"/>
+      <c r="C897" s="3"/>
     </row>
     <row r="898">
-      <c r="C898" s="4"/>
+      <c r="C898" s="3"/>
     </row>
     <row r="899">
-      <c r="C899" s="4"/>
+      <c r="C899" s="3"/>
     </row>
     <row r="900">
-      <c r="C900" s="4"/>
+      <c r="C900" s="3"/>
     </row>
     <row r="901">
-      <c r="C901" s="4"/>
+      <c r="C901" s="3"/>
     </row>
     <row r="902">
-      <c r="C902" s="4"/>
+      <c r="C902" s="3"/>
     </row>
     <row r="903">
-      <c r="C903" s="4"/>
+      <c r="C903" s="3"/>
     </row>
     <row r="904">
-      <c r="C904" s="4"/>
+      <c r="C904" s="3"/>
     </row>
     <row r="905">
-      <c r="C905" s="4"/>
+      <c r="C905" s="3"/>
     </row>
     <row r="906">
-      <c r="C906" s="4"/>
+      <c r="C906" s="3"/>
     </row>
     <row r="907">
-      <c r="C907" s="4"/>
+      <c r="C907" s="3"/>
     </row>
     <row r="908">
-      <c r="C908" s="4"/>
+      <c r="C908" s="3"/>
     </row>
     <row r="909">
-      <c r="C909" s="4"/>
+      <c r="C909" s="3"/>
     </row>
     <row r="910">
-      <c r="C910" s="4"/>
+      <c r="C910" s="3"/>
     </row>
     <row r="911">
-      <c r="C911" s="4"/>
+      <c r="C911" s="3"/>
     </row>
     <row r="912">
-      <c r="C912" s="4"/>
+      <c r="C912" s="3"/>
     </row>
     <row r="913">
-      <c r="C913" s="4"/>
+      <c r="C913" s="3"/>
     </row>
     <row r="914">
-      <c r="C914" s="4"/>
+      <c r="C914" s="3"/>
     </row>
     <row r="915">
-      <c r="C915" s="4"/>
+      <c r="C915" s="3"/>
     </row>
     <row r="916">
-      <c r="C916" s="4"/>
+      <c r="C916" s="3"/>
     </row>
     <row r="917">
-      <c r="C917" s="4"/>
+      <c r="C917" s="3"/>
     </row>
     <row r="918">
-      <c r="C918" s="4"/>
+      <c r="C918" s="3"/>
     </row>
     <row r="919">
-      <c r="C919" s="4"/>
+      <c r="C919" s="3"/>
     </row>
     <row r="920">
-      <c r="C920" s="4"/>
+      <c r="C920" s="3"/>
     </row>
     <row r="921">
-      <c r="C921" s="4"/>
+      <c r="C921" s="3"/>
     </row>
     <row r="922">
-      <c r="C922" s="4"/>
+      <c r="C922" s="3"/>
     </row>
     <row r="923">
-      <c r="C923" s="4"/>
+      <c r="C923" s="3"/>
     </row>
     <row r="924">
-      <c r="C924" s="4"/>
+      <c r="C924" s="3"/>
     </row>
     <row r="925">
-      <c r="C925" s="4"/>
+      <c r="C925" s="3"/>
     </row>
     <row r="926">
-      <c r="C926" s="4"/>
+      <c r="C926" s="3"/>
     </row>
     <row r="927">
-      <c r="C927" s="4"/>
+      <c r="C927" s="3"/>
     </row>
     <row r="928">
-      <c r="C928" s="4"/>
+      <c r="C928" s="3"/>
     </row>
     <row r="929">
-      <c r="C929" s="4"/>
+      <c r="C929" s="3"/>
     </row>
     <row r="930">
-      <c r="C930" s="4"/>
+      <c r="C930" s="3"/>
     </row>
     <row r="931">
-      <c r="C931" s="4"/>
+      <c r="C931" s="3"/>
     </row>
     <row r="932">
-      <c r="C932" s="4"/>
+      <c r="C932" s="3"/>
     </row>
     <row r="933">
-      <c r="C933" s="4"/>
+      <c r="C933" s="3"/>
     </row>
     <row r="934">
-      <c r="C934" s="4"/>
+      <c r="C934" s="3"/>
     </row>
     <row r="935">
-      <c r="C935" s="4"/>
+      <c r="C935" s="3"/>
     </row>
     <row r="936">
-      <c r="C936" s="4"/>
+      <c r="C936" s="3"/>
     </row>
     <row r="937">
-      <c r="C937" s="4"/>
+      <c r="C937" s="3"/>
     </row>
     <row r="938">
-      <c r="C938" s="4"/>
+      <c r="C938" s="3"/>
     </row>
     <row r="939">
-      <c r="C939" s="4"/>
+      <c r="C939" s="3"/>
     </row>
     <row r="940">
-      <c r="C940" s="4"/>
+      <c r="C940" s="3"/>
     </row>
     <row r="941">
-      <c r="C941" s="4"/>
+      <c r="C941" s="3"/>
     </row>
     <row r="942">
-      <c r="C942" s="4"/>
+      <c r="C942" s="3"/>
     </row>
     <row r="943">
-      <c r="C943" s="4"/>
+      <c r="C943" s="3"/>
     </row>
     <row r="944">
-      <c r="C944" s="4"/>
+      <c r="C944" s="3"/>
     </row>
     <row r="945">
-      <c r="C945" s="4"/>
+      <c r="C945" s="3"/>
     </row>
     <row r="946">
-      <c r="C946" s="4"/>
+      <c r="C946" s="3"/>
     </row>
     <row r="947">
-      <c r="C947" s="4"/>
+      <c r="C947" s="3"/>
     </row>
     <row r="948">
-      <c r="C948" s="4"/>
+      <c r="C948" s="3"/>
     </row>
     <row r="949">
-      <c r="C949" s="4"/>
+      <c r="C949" s="3"/>
     </row>
     <row r="950">
-      <c r="C950" s="4"/>
+      <c r="C950" s="3"/>
     </row>
     <row r="951">
-      <c r="C951" s="4"/>
+      <c r="C951" s="3"/>
     </row>
     <row r="952">
-      <c r="C952" s="4"/>
+      <c r="C952" s="3"/>
     </row>
     <row r="953">
-      <c r="C953" s="4"/>
+      <c r="C953" s="3"/>
     </row>
     <row r="954">
-      <c r="C954" s="4"/>
+      <c r="C954" s="3"/>
     </row>
     <row r="955">
-      <c r="C955" s="4"/>
+      <c r="C955" s="3"/>
     </row>
     <row r="956">
-      <c r="C956" s="4"/>
+      <c r="C956" s="3"/>
     </row>
     <row r="957">
-      <c r="C957" s="4"/>
+      <c r="C957" s="3"/>
     </row>
     <row r="958">
-      <c r="C958" s="4"/>
+      <c r="C958" s="3"/>
     </row>
     <row r="959">
-      <c r="C959" s="4"/>
+      <c r="C959" s="3"/>
     </row>
     <row r="960">
-      <c r="C960" s="4"/>
+      <c r="C960" s="3"/>
     </row>
     <row r="961">
-      <c r="C961" s="4"/>
+      <c r="C961" s="3"/>
     </row>
     <row r="962">
-      <c r="C962" s="4"/>
+      <c r="C962" s="3"/>
     </row>
     <row r="963">
-      <c r="C963" s="4"/>
+      <c r="C963" s="3"/>
     </row>
     <row r="964">
-      <c r="C964" s="4"/>
+      <c r="C964" s="3"/>
     </row>
     <row r="965">
-      <c r="C965" s="4"/>
+      <c r="C965" s="3"/>
     </row>
     <row r="966">
-      <c r="C966" s="4"/>
+      <c r="C966" s="3"/>
     </row>
     <row r="967">
-      <c r="C967" s="4"/>
+      <c r="C967" s="3"/>
     </row>
     <row r="968">
-      <c r="C968" s="4"/>
+      <c r="C968" s="3"/>
     </row>
     <row r="969">
-      <c r="C969" s="4"/>
+      <c r="C969" s="3"/>
     </row>
     <row r="970">
-      <c r="C970" s="4"/>
+      <c r="C970" s="3"/>
     </row>
     <row r="971">
-      <c r="C971" s="4"/>
+      <c r="C971" s="3"/>
     </row>
     <row r="972">
-      <c r="C972" s="4"/>
+      <c r="C972" s="3"/>
     </row>
     <row r="973">
-      <c r="C973" s="4"/>
+      <c r="C973" s="3"/>
     </row>
     <row r="974">
-      <c r="C974" s="4"/>
+      <c r="C974" s="3"/>
     </row>
     <row r="975">
-      <c r="C975" s="4"/>
+      <c r="C975" s="3"/>
     </row>
     <row r="976">
-      <c r="C976" s="4"/>
+      <c r="C976" s="3"/>
     </row>
     <row r="977">
-      <c r="C977" s="4"/>
+      <c r="C977" s="3"/>
     </row>
     <row r="978">
-      <c r="C978" s="4"/>
+      <c r="C978" s="3"/>
     </row>
     <row r="979">
-      <c r="C979" s="4"/>
+      <c r="C979" s="3"/>
     </row>
     <row r="980">
-      <c r="C980" s="4"/>
+      <c r="C980" s="3"/>
     </row>
     <row r="981">
-      <c r="C981" s="4"/>
+      <c r="C981" s="3"/>
     </row>
     <row r="982">
-      <c r="C982" s="4"/>
+      <c r="C982" s="3"/>
     </row>
     <row r="983">
-      <c r="C983" s="4"/>
+      <c r="C983" s="3"/>
     </row>
     <row r="984">
-      <c r="C984" s="4"/>
+      <c r="C984" s="3"/>
     </row>
     <row r="985">
-      <c r="C985" s="4"/>
+      <c r="C985" s="3"/>
     </row>
     <row r="986">
-      <c r="C986" s="4"/>
+      <c r="C986" s="3"/>
     </row>
     <row r="987">
-      <c r="C987" s="4"/>
+      <c r="C987" s="3"/>
     </row>
     <row r="988">
-      <c r="C988" s="4"/>
+      <c r="C988" s="3"/>
     </row>
     <row r="989">
-      <c r="C989" s="4"/>
+      <c r="C989" s="3"/>
     </row>
     <row r="990">
-      <c r="C990" s="4"/>
+      <c r="C990" s="3"/>
     </row>
     <row r="991">
-      <c r="C991" s="4"/>
+      <c r="C991" s="3"/>
     </row>
     <row r="992">
-      <c r="C992" s="4"/>
+      <c r="C992" s="3"/>
     </row>
     <row r="993">
-      <c r="C993" s="4"/>
+      <c r="C993" s="3"/>
     </row>
     <row r="994">
-      <c r="C994" s="4"/>
+      <c r="C994" s="3"/>
     </row>
     <row r="995">
-      <c r="C995" s="4"/>
+      <c r="C995" s="3"/>
     </row>
     <row r="996">
-      <c r="C996" s="4"/>
+      <c r="C996" s="3"/>
     </row>
     <row r="997">
-      <c r="C997" s="4"/>
+      <c r="C997" s="3"/>
     </row>
     <row r="998">
-      <c r="C998" s="4"/>
+      <c r="C998" s="3"/>
     </row>
     <row r="999">
-      <c r="C999" s="4"/>
+      <c r="C999" s="3"/>
     </row>
     <row r="1000">
-      <c r="C1000" s="4"/>
+      <c r="C1000" s="3"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -1,27 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
-    <t>Name</t>
+    <t>Student Name</t>
   </si>
   <si>
     <t>Grade</t>
@@ -126,16 +118,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -146,43 +142,38 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="4">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -372,358 +363,1331 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="12.63"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B3" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B4" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B5" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B6" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B8" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B9" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B10" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B11" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="B12" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B15" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B16" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B17" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="B21" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="B22" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D23" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B24" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
-        <v>4</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="B25" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="B26" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B27" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28">
-        <v>6</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B28" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B29">
-        <v>6</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="B29" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B30">
-        <v>6</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B30" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-    </row>
+      <c r="B31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/students.xlsx
+++ b/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Student Name</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t xml:space="preserve">Iyad Ibrahim Mostafa </t>
+  </si>
+  <si>
+    <t>Youssef Islam ElFaham</t>
+  </si>
+  <si>
+    <t>Seif Elfaham</t>
   </si>
 </sst>
 </file>
@@ -151,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -160,6 +166,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -715,8 +724,28 @@
         <v>2.0</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D33" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Student Name</t>
   </si>
@@ -25,100 +25,127 @@
     <t>Équipe</t>
   </si>
   <si>
-    <t>Mazen Mohamed Salah</t>
-  </si>
-  <si>
-    <t>Andrew Bishoy</t>
-  </si>
-  <si>
-    <t>Aly Hagag</t>
-  </si>
-  <si>
-    <t>Mahmoud Abdelrahman</t>
-  </si>
-  <si>
-    <t>Andrea Rimon</t>
-  </si>
-  <si>
-    <t>Ahmed Aboulella</t>
-  </si>
-  <si>
-    <t>Adham Ahmed Sherif</t>
-  </si>
-  <si>
-    <t>Zein Ahmed Sherif</t>
-  </si>
-  <si>
-    <t>Mohamed Hisham</t>
-  </si>
-  <si>
-    <t>Ziad Moataz El-Sayed</t>
-  </si>
-  <si>
-    <t>Khalil Ahmed Rami</t>
-  </si>
-  <si>
-    <t>Ahmed El-Sayed Kamel</t>
-  </si>
-  <si>
-    <t>Selim Mohamed Serag</t>
-  </si>
-  <si>
-    <t>Aly Amr Adel</t>
-  </si>
-  <si>
-    <t>Abdelrahman Ahmed Abdelkhalek</t>
-  </si>
-  <si>
-    <t>Youssef Islam</t>
-  </si>
-  <si>
-    <t>Ahmed Moatasem</t>
-  </si>
-  <si>
-    <t>Shady Isak</t>
-  </si>
-  <si>
-    <t>Evan Adib</t>
-  </si>
-  <si>
-    <t>Steven Sameh Fawzy</t>
-  </si>
-  <si>
-    <t>Eric Amir Shenouda</t>
-  </si>
-  <si>
-    <t>Tomas Elbert Samir</t>
-  </si>
-  <si>
-    <t>Roben Sameh Farid</t>
-  </si>
-  <si>
-    <t>Mahmoud Mohamed Nehro</t>
-  </si>
-  <si>
-    <t>Dave Gerges</t>
-  </si>
-  <si>
-    <t>Youssef Mazen</t>
-  </si>
-  <si>
-    <t>Abdelrahman Moatasem</t>
-  </si>
-  <si>
-    <t>Jovany Michael</t>
-  </si>
-  <si>
-    <t>Adham Ibrahim Mostafa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyad Ibrahim Mostafa </t>
-  </si>
-  <si>
-    <t>Youssef Islam ElFaham</t>
-  </si>
-  <si>
-    <t>Seif Elfaham</t>
+    <t>Fatima Hassan Ahmed Salam</t>
+  </si>
+  <si>
+    <t>01226374350</t>
+  </si>
+  <si>
+    <t>Larine Wagdy Galal</t>
+  </si>
+  <si>
+    <t>01003992399</t>
+  </si>
+  <si>
+    <t>Taline Wagdy Galal</t>
+  </si>
+  <si>
+    <t>Kinda Diaa Mohamed</t>
+  </si>
+  <si>
+    <t>01070360309</t>
+  </si>
+  <si>
+    <t>Ganna Ahmed</t>
+  </si>
+  <si>
+    <t>01060507486</t>
+  </si>
+  <si>
+    <t>Basilia Ashraf Gaber</t>
+  </si>
+  <si>
+    <t>09483771220</t>
+  </si>
+  <si>
+    <t>Lojaine Mostafa</t>
+  </si>
+  <si>
+    <t>01553766555</t>
+  </si>
+  <si>
+    <t>Celine Mohamed</t>
+  </si>
+  <si>
+    <t>19888961000</t>
+  </si>
+  <si>
+    <t>Lilly Waël</t>
+  </si>
+  <si>
+    <t>01223985410</t>
+  </si>
+  <si>
+    <t>Karen Ahmed Mohsen</t>
+  </si>
+  <si>
+    <t>23167461220</t>
+  </si>
+  <si>
+    <t>Jana Mahmoud Ibrahim</t>
+  </si>
+  <si>
+    <t>01280170279</t>
+  </si>
+  <si>
+    <t>Hana Mohamed Saad</t>
+  </si>
+  <si>
+    <t>01001042544</t>
+  </si>
+  <si>
+    <t>Lara Ahmed Mohamadeine</t>
+  </si>
+  <si>
+    <t>01062469828</t>
+  </si>
+  <si>
+    <t>Talia Helaly</t>
+  </si>
+  <si>
+    <t>08223111090</t>
+  </si>
+  <si>
+    <t>Nadine Helaly</t>
+  </si>
+  <si>
+    <t>Cérine Negm</t>
+  </si>
+  <si>
+    <t>Mariam Abdallah Mostafa Abdallah El Sokary</t>
+  </si>
+  <si>
+    <t>01096554189</t>
+  </si>
+  <si>
+    <t>Layan Hazem</t>
+  </si>
+  <si>
+    <t>01013333234</t>
+  </si>
+  <si>
+    <t>Farida Mohamed Saleh Shalaby</t>
+  </si>
+  <si>
+    <t>01006558939</t>
+  </si>
+  <si>
+    <t>Jolie Mostafa Mohamed</t>
+  </si>
+  <si>
+    <t>01224359262</t>
+  </si>
+  <si>
+    <t>Talia Etaby</t>
+  </si>
+  <si>
+    <t>Farida Ahmed Abd El Fatah Abd El Aziz</t>
+  </si>
+  <si>
+    <t>01554519960</t>
+  </si>
+  <si>
+    <t>monaya mohamed hassan</t>
   </si>
 </sst>
 </file>
@@ -127,19 +154,19 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -151,8 +178,22 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
@@ -161,14 +202,14 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -198,40 +239,40 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -378,15 +419,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="1" max="6" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -396,356 +436,335 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D2" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4">
         <v>2.0</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D4" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4">
         <v>1.0</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D5" s="3">
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4">
         <v>1.0</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D8" s="3">
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4">
         <v>1.0</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4">
         <v>1.0</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3">
         <v>6.0</v>
       </c>
-      <c r="D11" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="4">
         <v>2.0</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B13" s="3">
         <v>4.0</v>
       </c>
-      <c r="D13" s="3">
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="4">
         <v>2.0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D14" s="3">
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="C16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="4">
         <v>3.0</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="B17" s="3">
         <v>6.0</v>
       </c>
-      <c r="D17" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>20</v>
+      <c r="C17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B18" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D18" s="3">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
+      <c r="C18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B19" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D19" s="3">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
+      <c r="C19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B20" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D20" s="3">
-        <v>3.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
+      <c r="A21" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B21" s="3">
         <v>4.0</v>
       </c>
-      <c r="D21" s="3">
-        <v>3.0</v>
+      <c r="C21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>24</v>
+      <c r="A22" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="B22" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3.0</v>
+        <v>6.0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
+      <c r="A23" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B23" s="3">
         <v>4.0</v>
       </c>
-      <c r="D23" s="3">
+      <c r="C23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="4">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D24" s="3">
+      <c r="E24" s="4">
         <v>3.0</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D25" s="3">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D27" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="D30" s="3">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="D32" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="D33" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Student Name</t>
   </si>
@@ -25,127 +25,79 @@
     <t>Équipe</t>
   </si>
   <si>
-    <t>Fatima Hassan Ahmed Salam</t>
-  </si>
-  <si>
-    <t>01226374350</t>
-  </si>
-  <si>
-    <t>Larine Wagdy Galal</t>
-  </si>
-  <si>
-    <t>01003992399</t>
-  </si>
-  <si>
-    <t>Taline Wagdy Galal</t>
-  </si>
-  <si>
-    <t>Kinda Diaa Mohamed</t>
-  </si>
-  <si>
-    <t>01070360309</t>
-  </si>
-  <si>
-    <t>Ganna Ahmed</t>
-  </si>
-  <si>
-    <t>01060507486</t>
-  </si>
-  <si>
-    <t>Basilia Ashraf Gaber</t>
-  </si>
-  <si>
-    <t>09483771220</t>
-  </si>
-  <si>
-    <t>Lojaine Mostafa</t>
-  </si>
-  <si>
-    <t>01553766555</t>
-  </si>
-  <si>
-    <t>Celine Mohamed</t>
-  </si>
-  <si>
-    <t>19888961000</t>
-  </si>
-  <si>
-    <t>Lilly Waël</t>
-  </si>
-  <si>
-    <t>01223985410</t>
-  </si>
-  <si>
-    <t>Karen Ahmed Mohsen</t>
-  </si>
-  <si>
-    <t>23167461220</t>
-  </si>
-  <si>
-    <t>Jana Mahmoud Ibrahim</t>
-  </si>
-  <si>
-    <t>01280170279</t>
-  </si>
-  <si>
-    <t>Hana Mohamed Saad</t>
-  </si>
-  <si>
-    <t>01001042544</t>
-  </si>
-  <si>
-    <t>Lara Ahmed Mohamadeine</t>
-  </si>
-  <si>
-    <t>01062469828</t>
-  </si>
-  <si>
-    <t>Talia Helaly</t>
-  </si>
-  <si>
-    <t>08223111090</t>
-  </si>
-  <si>
-    <t>Nadine Helaly</t>
-  </si>
-  <si>
-    <t>Cérine Negm</t>
-  </si>
-  <si>
-    <t>Mariam Abdallah Mostafa Abdallah El Sokary</t>
-  </si>
-  <si>
-    <t>01096554189</t>
-  </si>
-  <si>
-    <t>Layan Hazem</t>
-  </si>
-  <si>
-    <t>01013333234</t>
-  </si>
-  <si>
-    <t>Farida Mohamed Saleh Shalaby</t>
-  </si>
-  <si>
-    <t>01006558939</t>
-  </si>
-  <si>
-    <t>Jolie Mostafa Mohamed</t>
-  </si>
-  <si>
-    <t>01224359262</t>
-  </si>
-  <si>
-    <t>Talia Etaby</t>
-  </si>
-  <si>
-    <t>Farida Ahmed Abd El Fatah Abd El Aziz</t>
-  </si>
-  <si>
-    <t>01554519960</t>
-  </si>
-  <si>
-    <t>monaya mohamed hassan</t>
+    <t>Layan Emad-Eldin</t>
+  </si>
+  <si>
+    <t>Layan Ahmed</t>
+  </si>
+  <si>
+    <t>Layla Mohamed</t>
+  </si>
+  <si>
+    <t>Farah Hamdi</t>
+  </si>
+  <si>
+    <t>Hana Ahmed</t>
+  </si>
+  <si>
+    <t>Farida Momen</t>
+  </si>
+  <si>
+    <t>Dora Ahmed</t>
+  </si>
+  <si>
+    <t>Nadin Tamer</t>
+  </si>
+  <si>
+    <t>Khadija Ahmed</t>
+  </si>
+  <si>
+    <t>Hala Mostafa</t>
+  </si>
+  <si>
+    <t>Dora Mohamed</t>
+  </si>
+  <si>
+    <t>Ayda Ahmed</t>
+  </si>
+  <si>
+    <t>Dalia Mohamed</t>
+  </si>
+  <si>
+    <t>Lylian Amir</t>
+  </si>
+  <si>
+    <t>Naira Eissa</t>
+  </si>
+  <si>
+    <t>Byonsé Samuel</t>
+  </si>
+  <si>
+    <t>Layla Adel</t>
+  </si>
+  <si>
+    <t>Fagr Hamdi</t>
+  </si>
+  <si>
+    <t>Lily Ahmed</t>
+  </si>
+  <si>
+    <t>Layan Mohamed</t>
+  </si>
+  <si>
+    <t>Lily Amr</t>
+  </si>
+  <si>
+    <t>Razan Ahmed</t>
+  </si>
+  <si>
+    <t>Farida Mohamed</t>
+  </si>
+  <si>
+    <t>Gamila Mohamed</t>
+  </si>
+  <si>
+    <t>Hala Mohamed</t>
   </si>
 </sst>
 </file>
@@ -160,9 +112,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -178,37 +129,22 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,7 +359,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="8.71"/>
+    <col customWidth="1" min="1" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -436,7 +372,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -444,320 +380,127 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2.0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="4">
-        <v>3.0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="4">
-        <v>3.0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="4">
-        <v>3.0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1.0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1.0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1.0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4">
-        <v>2.0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1.0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="4">
-        <v>2.0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1.0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2.0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2.0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3.0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="4">
-        <v>2.0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3.0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="4">
-        <v>3.0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="4">
-        <v>2.0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="4">
-        <v>1.0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2.0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="4">
-        <v>1.0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="E24" s="4">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
+      <c r="A24" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>

--- a/students.xlsx
+++ b/students.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>Student Name</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Layan Emad-Eldin</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Layan Ahmed</t>
@@ -135,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -146,6 +149,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -380,125 +386,350 @@
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
